--- a/outputs/QLD_mlf.xlsx
+++ b/outputs/QLD_mlf.xlsx
@@ -1587,8 +1587,10 @@
           <t>KIDSPHG2</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n">
-        <v/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>KIDSPHES</t>
+        </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
@@ -2143,8 +2145,10 @@
           <t>CALL_A_4</t>
         </is>
       </c>
-      <c r="B30" s="2" t="n">
-        <v/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>CALLIDE</t>
+        </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
@@ -2187,8 +2191,10 @@
           <t>CALLNL4</t>
         </is>
       </c>
-      <c r="B31" s="2" t="n">
-        <v/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>CALLIDE</t>
+        </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
@@ -2479,8 +2485,10 @@
           <t>CALLNL1</t>
         </is>
       </c>
-      <c r="B36" s="2" t="n">
-        <v/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>CALLIDE</t>
+        </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
@@ -2659,8 +2667,10 @@
           <t>STANNL1</t>
         </is>
       </c>
-      <c r="B39" s="2" t="n">
-        <v/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>STANWELL</t>
+        </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
@@ -2881,8 +2891,10 @@
           <t>GLADNL1</t>
         </is>
       </c>
-      <c r="B43" s="2" t="n">
-        <v/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>G/STONE</t>
+        </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
@@ -5163,8 +5175,10 @@
           <t>TARNL1</t>
         </is>
       </c>
-      <c r="B83" s="2" t="n">
-        <v/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>TARONG</t>
+        </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
@@ -7321,8 +7335,10 @@
           <t>DG_QLD1</t>
         </is>
       </c>
-      <c r="B121" s="2" t="n">
-        <v/>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>DG_QLD1</t>
+        </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
@@ -7563,8 +7579,10 @@
           <t>PIONEER</t>
         </is>
       </c>
-      <c r="B125" s="2" t="n">
-        <v/>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>PIONEER</t>
+        </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
@@ -8079,8 +8097,10 @@
           <t>VICMILL1</t>
         </is>
       </c>
-      <c r="B134" s="2" t="n">
-        <v/>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>VICMILL</t>
+        </is>
       </c>
       <c r="C134" s="2" t="n">
         <v/>
@@ -8135,8 +8155,10 @@
           <t>SUNCOAST</t>
         </is>
       </c>
-      <c r="B135" s="2" t="n">
-        <v/>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>SUNCOAST</t>
+        </is>
       </c>
       <c r="C135" s="2" t="n">
         <v/>
@@ -8165,8 +8187,10 @@
           <t>STHBKTEC</t>
         </is>
       </c>
-      <c r="B136" s="2" t="n">
-        <v/>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>STHBKTEC</t>
+        </is>
       </c>
       <c r="C136" s="2" t="n">
         <v/>
@@ -8201,8 +8225,10 @@
           <t>EDLRGNRD</t>
         </is>
       </c>
-      <c r="B137" s="2" t="n">
-        <v/>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>EDLRGNRD</t>
+        </is>
       </c>
       <c r="C137" s="2" t="n">
         <v/>
@@ -8239,8 +8265,10 @@
           <t>ROCHEDAL</t>
         </is>
       </c>
-      <c r="B138" s="2" t="n">
-        <v/>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>ROCHEDAL</t>
+        </is>
       </c>
       <c r="C138" s="2" t="n">
         <v/>
@@ -8321,8 +8349,10 @@
           <t>MACKAYGT</t>
         </is>
       </c>
-      <c r="B140" s="2" t="n">
-        <v/>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Mackay Gas Turbine</t>
+        </is>
       </c>
       <c r="C140" s="2" t="n">
         <v/>
@@ -8361,8 +8391,10 @@
           <t>DAANDINE</t>
         </is>
       </c>
-      <c r="B141" s="2" t="n">
-        <v/>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>DAANDINE</t>
+        </is>
       </c>
       <c r="C141" s="2" t="n">
         <v/>
@@ -8403,8 +8435,10 @@
           <t>WIVENSH</t>
         </is>
       </c>
-      <c r="B142" s="2" t="n">
-        <v/>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>WIVENSH</t>
+        </is>
       </c>
       <c r="C142" s="2" t="n">
         <v/>
@@ -8449,8 +8483,10 @@
           <t>WDBESSG1</t>
         </is>
       </c>
-      <c r="B143" s="2" t="n">
-        <v/>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>WDBESS</t>
+        </is>
       </c>
       <c r="C143" s="2" t="n">
         <v/>
@@ -8481,8 +8517,10 @@
           <t>CHBESSG1</t>
         </is>
       </c>
-      <c r="B144" s="2" t="n">
-        <v/>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>CHBESS</t>
+        </is>
       </c>
       <c r="C144" s="2" t="n">
         <v/>
@@ -8513,8 +8551,10 @@
           <t>WANDBG1</t>
         </is>
       </c>
-      <c r="B145" s="2" t="n">
-        <v/>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>WANDBESS</t>
+        </is>
       </c>
       <c r="C145" s="2" t="n">
         <v/>
@@ -8549,8 +8589,10 @@
           <t>BBATTERY</t>
         </is>
       </c>
-      <c r="B146" s="2" t="n">
-        <v/>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>BBATTERY</t>
+        </is>
       </c>
       <c r="C146" s="2" t="n">
         <v/>
@@ -14323,8 +14365,10 @@
           <t>KIDSPHG2</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
-        <v/>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>KIDSPHES</t>
+        </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>

--- a/outputs/QLD_mlf.xlsx
+++ b/outputs/QLD_mlf.xlsx
@@ -1589,13 +1589,17 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>KIDSPHES</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D20" s="2" t="inlineStr"/>
+          <t>Kidston Hydro Project</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Hydro</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>126</v>
+      </c>
       <c r="E20" s="4" t="inlineStr"/>
       <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="inlineStr"/>
@@ -2147,13 +2151,17 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>CALLIDE</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D30" s="2" t="inlineStr"/>
+          <t>Callide Power Station</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>30</v>
+      </c>
       <c r="E30" s="4" t="n">
         <v>0.9563</v>
       </c>
@@ -2193,13 +2201,13 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>CALLIDE</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D31" s="2" t="inlineStr"/>
+          <t>Callide Power Station</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr"/>
+      <c r="D31" s="3" t="n">
+        <v>30</v>
+      </c>
       <c r="E31" s="4" t="n">
         <v>0.9563</v>
       </c>
@@ -2487,13 +2495,17 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>CALLIDE</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D36" s="2" t="inlineStr"/>
+          <t>Callide Power Station</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>25</v>
+      </c>
       <c r="E36" s="4" t="n">
         <v>0.959</v>
       </c>
@@ -2669,13 +2681,17 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>STANWELL</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D39" s="2" t="inlineStr"/>
+          <t>STANWELL POWER STATION</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>25</v>
+      </c>
       <c r="E39" s="4" t="n">
         <v>0.9897</v>
       </c>
@@ -2893,13 +2909,17 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>G/STONE</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D43" s="2" t="inlineStr"/>
+          <t>GLADSTONE POWER STATION</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>25</v>
+      </c>
       <c r="E43" s="4" t="n">
         <v>0.9855</v>
       </c>
@@ -5177,13 +5197,17 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>TARONG</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D83" s="2" t="inlineStr"/>
+          <t>TARONG POWER STATION</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>25</v>
+      </c>
       <c r="E83" s="4" t="n">
         <v>0.9711</v>
       </c>
@@ -7337,13 +7361,13 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>DG_QLD1</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D121" s="2" t="inlineStr"/>
+          <t>QLD1 Dummy Generator</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr"/>
+      <c r="D121" s="3" t="n">
+        <v>3000</v>
+      </c>
       <c r="E121" s="4" t="n">
         <v>1</v>
       </c>
@@ -7581,7 +7605,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>Pioneer Sugar Mill</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
@@ -8099,13 +8123,17 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>VICMILL</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D134" s="2" t="inlineStr"/>
+          <t>Victoria Mill</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Other Renewable</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>24</v>
+      </c>
       <c r="E134" s="4" t="n">
         <v>1.1403</v>
       </c>
@@ -8157,13 +8185,13 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>SUNCOAST</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D135" s="2" t="inlineStr"/>
+          <t>Suncoast Gold Macadamias</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr"/>
+      <c r="D135" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="E135" s="4" t="n">
         <v>1.0124</v>
       </c>
@@ -8189,13 +8217,17 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>STHBKTEC</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D136" s="2" t="inlineStr"/>
+          <t>Southbank Institute Of Technology Unit 1 Plant</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="E136" s="4" t="n">
         <v>1.0141</v>
       </c>
@@ -8227,13 +8259,17 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>EDLRGNRD</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D137" s="2" t="inlineStr"/>
+          <t>Roghan Road LFG Power Plant</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Other Renewable</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="E137" s="4" t="n">
         <v>1.0057</v>
       </c>
@@ -8267,13 +8303,17 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>ROCHEDAL</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D138" s="2" t="inlineStr"/>
+          <t>Rochedale Renewable Energy Facility</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Other Renewable</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="n">
+        <v>4</v>
+      </c>
       <c r="E138" s="4" t="n">
         <v>1.0067</v>
       </c>
@@ -8393,13 +8433,17 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>DAANDINE</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D141" s="2" t="inlineStr"/>
+          <t>Daandine Power Station</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="n">
+        <v>33</v>
+      </c>
       <c r="E141" s="4" t="n">
         <v>0.9747</v>
       </c>
@@ -8437,13 +8481,17 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>WIVENSH</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D142" s="2" t="inlineStr"/>
+          <t>WIVENHOE SMALL HYDRO</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Hydro</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="E142" s="4" t="n">
         <v>0.9945000000000001</v>
       </c>
@@ -8485,13 +8533,17 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>WDBESS</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D143" s="2" t="inlineStr"/>
+          <t>Western Downs Battery Energy Storage System (BESS)</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="n">
+        <v>272</v>
+      </c>
       <c r="E143" s="4" t="inlineStr"/>
       <c r="F143" s="4" t="inlineStr"/>
       <c r="G143" s="4" t="inlineStr"/>
@@ -8519,13 +8571,17 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>CHBESS</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D144" s="2" t="inlineStr"/>
+          <t>Chinchilla BESS</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="n">
+        <v>134</v>
+      </c>
       <c r="E144" s="4" t="inlineStr"/>
       <c r="F144" s="4" t="inlineStr"/>
       <c r="G144" s="4" t="inlineStr"/>
@@ -8553,13 +8609,17 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>WANDBESS</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D145" s="2" t="inlineStr"/>
+          <t>Wandoan BESS</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="n">
+        <v>123</v>
+      </c>
       <c r="E145" s="4" t="inlineStr"/>
       <c r="F145" s="4" t="inlineStr"/>
       <c r="G145" s="4" t="inlineStr"/>
@@ -8591,7 +8651,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>BBATTERY</t>
+          <t>Bouldercombe Battery Project</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
@@ -14367,11 +14427,13 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>KIDSPHES</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v/>
+          <t>Kidston Hydro Project</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Hydro</t>
+        </is>
       </c>
       <c r="D3" s="4" t="n">
         <v>0.894</v>

--- a/outputs/QLD_mlf.xlsx
+++ b/outputs/QLD_mlf.xlsx
@@ -1024,12 +1024,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>KSP1</t>
+          <t>HUGSF1</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Kidston Solar Project Phase One</t>
+          <t>Hughenden Solar Farm</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>50</v>
+        <v>20.97</v>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
       <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="4" t="n">
-        <v>1.0149</v>
+        <v>1.0115</v>
       </c>
       <c r="H10" s="4" t="n">
         <v>0.8842</v>
@@ -1140,12 +1140,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>HUGSF1</t>
+          <t>KSP1</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Hughenden Solar Farm</t>
+          <t>Kidston Solar Project Phase One</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>20.97</v>
+        <v>50</v>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
       <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="4" t="n">
-        <v>1.0115</v>
+        <v>1.0149</v>
       </c>
       <c r="H12" s="4" t="n">
         <v>0.8842</v>
@@ -1354,12 +1354,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>LRSF1</t>
+          <t>CLERMSF1</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Longreach Solar Farm</t>
+          <t>Clermont Solar Farm</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1368,15 +1368,13 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>17</v>
+        <v>92.5</v>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
       <c r="F16" s="4" t="inlineStr"/>
-      <c r="G16" s="4" t="n">
-        <v>0.9689</v>
-      </c>
+      <c r="G16" s="4" t="inlineStr"/>
       <c r="H16" s="4" t="n">
-        <v>0.8934</v>
+        <v>0.8862</v>
       </c>
       <c r="I16" s="4" t="n">
         <v>0.8735000000000001</v>
@@ -1472,12 +1470,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>CLERMSF1</t>
+          <t>LRSF1</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Clermont Solar Farm</t>
+          <t>Longreach Solar Farm</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1486,13 +1484,15 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>92.5</v>
+        <v>17</v>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
       <c r="F18" s="4" t="inlineStr"/>
-      <c r="G18" s="4" t="inlineStr"/>
+      <c r="G18" s="4" t="n">
+        <v>0.9689</v>
+      </c>
       <c r="H18" s="4" t="n">
-        <v>0.8862</v>
+        <v>0.8934</v>
       </c>
       <c r="I18" s="4" t="n">
         <v>0.8735000000000001</v>
@@ -1737,13 +1737,21 @@
       <c r="K23" s="4" t="inlineStr"/>
       <c r="L23" s="4" t="inlineStr"/>
       <c r="M23" s="4" t="inlineStr"/>
-      <c r="N23" s="4" t="inlineStr"/>
-      <c r="O23" s="4" t="inlineStr"/>
+      <c r="N23" s="4" t="n">
+        <v>0.9528</v>
+      </c>
+      <c r="O23" s="4" t="n">
+        <v>0.9358</v>
+      </c>
       <c r="P23" s="4" t="n">
         <v>0.9008</v>
       </c>
-      <c r="Q23" s="4" t="inlineStr"/>
-      <c r="R23" s="5" t="inlineStr"/>
+      <c r="Q23" s="4" t="n">
+        <v>-0.035</v>
+      </c>
+      <c r="R23" s="5" t="n">
+        <v>-3.74</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2058,12 +2066,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>OAKY2</t>
+          <t>OAKYCREK</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Oaky Creek 2</t>
+          <t>Oaky Creek Power Station</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2072,7 +2080,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E29" s="4" t="n">
         <v>1.0373</v>
@@ -2120,12 +2128,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>OAKYCREK</t>
+          <t>OAKY2</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Oaky Creek Power Station</t>
+          <t>Oaky Creek 2</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2134,7 +2142,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E30" s="4" t="n">
         <v>1.0373</v>
@@ -2182,7 +2190,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>CALL_A_4</t>
+          <t>CALLNL4</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -2190,11 +2198,7 @@
           <t>Callide Power Station</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Fossil</t>
-        </is>
-      </c>
+      <c r="C31" s="2" t="inlineStr"/>
       <c r="D31" s="3" t="n">
         <v>30</v>
       </c>
@@ -2232,7 +2236,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>CALLNL4</t>
+          <t>CALL_A_4</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -2240,7 +2244,11 @@
           <t>Callide Power Station</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
       <c r="D32" s="3" t="n">
         <v>30</v>
       </c>
@@ -2278,7 +2286,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>STAN-3</t>
+          <t>STAN-1</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -2402,7 +2410,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>STAN-1</t>
+          <t>STAN-3</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2774,7 +2782,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>BRDDSF01</t>
+          <t>BRDDBES1</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2784,11 +2792,11 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>368</v>
+        <v>240</v>
       </c>
       <c r="E41" s="4" t="inlineStr"/>
       <c r="F41" s="4" t="inlineStr"/>
@@ -2816,7 +2824,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>BRDDBES1</t>
+          <t>BRDDSF01</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2826,11 +2834,11 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>240</v>
+        <v>368</v>
       </c>
       <c r="E42" s="4" t="inlineStr"/>
       <c r="F42" s="4" t="inlineStr"/>
@@ -2842,12 +2850,18 @@
       <c r="L42" s="4" t="inlineStr"/>
       <c r="M42" s="4" t="inlineStr"/>
       <c r="N42" s="4" t="inlineStr"/>
-      <c r="O42" s="4" t="inlineStr"/>
+      <c r="O42" s="4" t="n">
+        <v>0.929</v>
+      </c>
       <c r="P42" s="4" t="n">
         <v>0.9247</v>
       </c>
-      <c r="Q42" s="4" t="inlineStr"/>
-      <c r="R42" s="5" t="inlineStr"/>
+      <c r="Q42" s="4" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="R42" s="5" t="n">
+        <v>-0.46</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3100,7 +3114,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GSTONE6</t>
+          <t>GSTONE5</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -3162,7 +3176,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GSTONE5</t>
+          <t>GSTONE6</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -3812,12 +3826,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>SRSF1</t>
+          <t>CHILDSF1</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Susan River Solar Farm</t>
+          <t>Childers Solar Farm</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3826,7 +3840,7 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>85.26000000000001</v>
+        <v>64.38</v>
       </c>
       <c r="E60" s="4" t="inlineStr"/>
       <c r="F60" s="4" t="inlineStr"/>
@@ -3868,12 +3882,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>CHILDSF1</t>
+          <t>SRSF1</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Childers Solar Farm</t>
+          <t>Susan River Solar Farm</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3882,7 +3896,7 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>64.38</v>
+        <v>85.26000000000001</v>
       </c>
       <c r="E61" s="4" t="inlineStr"/>
       <c r="F61" s="4" t="inlineStr"/>
@@ -3986,7 +4000,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>MSTUART3</t>
+          <t>MSTUART2</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -4000,7 +4014,7 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="E63" s="4" t="n">
         <v>1.0156</v>
@@ -4048,7 +4062,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>MSTUART2</t>
+          <t>MSTUART3</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -4062,7 +4076,7 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="E64" s="4" t="n">
         <v>1.0156</v>
@@ -4394,7 +4408,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>KAREEYA4</t>
+          <t>KAREEYA2</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -4456,7 +4470,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>KAREEYA1</t>
+          <t>KAREEYA5</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -4470,7 +4484,7 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E72" s="4" t="n">
         <v>1.069</v>
@@ -4518,7 +4532,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>KAREEYA2</t>
+          <t>KAREEYA4</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -4642,7 +4656,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>KAREEYA5</t>
+          <t>KAREEYA1</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -4656,7 +4670,7 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E75" s="4" t="n">
         <v>1.069</v>
@@ -4990,12 +5004,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>BRAEMAR6</t>
+          <t>BRAEMAR2</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Braemar 2 Power Station</t>
+          <t>Braemar Power Station</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -5004,7 +5018,7 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E81" s="4" t="n">
         <v>0.9567</v>
@@ -5114,12 +5128,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>BRAEMAR1</t>
+          <t>BRAEMAR7</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Braemar Power Station</t>
+          <t>Braemar 2 Power Station</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -5128,7 +5142,7 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="E83" s="4" t="n">
         <v>0.9567</v>
@@ -5176,12 +5190,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>BRAEMAR2</t>
+          <t>BRAEMAR6</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Braemar Power Station</t>
+          <t>Braemar 2 Power Station</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -5190,7 +5204,7 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="E84" s="4" t="n">
         <v>0.9567</v>
@@ -5238,12 +5252,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>BRAEMAR7</t>
+          <t>BRAEMAR1</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Braemar 2 Power Station</t>
+          <t>Braemar Power Station</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -5252,7 +5266,7 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E85" s="4" t="n">
         <v>0.9567</v>
@@ -5530,7 +5544,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>TARONG#4</t>
+          <t>TARONG#3</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -5592,7 +5606,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>TARONG#3</t>
+          <t>TARONG#4</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -5977,13 +5991,21 @@
       <c r="K97" s="4" t="inlineStr"/>
       <c r="L97" s="4" t="inlineStr"/>
       <c r="M97" s="4" t="inlineStr"/>
-      <c r="N97" s="4" t="inlineStr"/>
-      <c r="O97" s="4" t="inlineStr"/>
+      <c r="N97" s="4" t="n">
+        <v>0.9837</v>
+      </c>
+      <c r="O97" s="4" t="n">
+        <v>0.9836</v>
+      </c>
       <c r="P97" s="4" t="n">
         <v>0.9772999999999999</v>
       </c>
-      <c r="Q97" s="4" t="inlineStr"/>
-      <c r="R97" s="5" t="inlineStr"/>
+      <c r="Q97" s="4" t="n">
+        <v>-0.0063</v>
+      </c>
+      <c r="R97" s="5" t="n">
+        <v>-0.64</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -6050,7 +6072,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>ROMA_7</t>
+          <t>ROMA_8</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -6112,7 +6134,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>ROMA_8</t>
+          <t>ROMA_7</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -6199,13 +6221,21 @@
       <c r="K101" s="4" t="inlineStr"/>
       <c r="L101" s="4" t="inlineStr"/>
       <c r="M101" s="4" t="inlineStr"/>
-      <c r="N101" s="4" t="inlineStr"/>
-      <c r="O101" s="4" t="inlineStr"/>
+      <c r="N101" s="4" t="n">
+        <v>0.9698</v>
+      </c>
+      <c r="O101" s="4" t="n">
+        <v>0.9851</v>
+      </c>
       <c r="P101" s="4" t="n">
         <v>0.9778</v>
       </c>
-      <c r="Q101" s="4" t="inlineStr"/>
-      <c r="R101" s="5" t="inlineStr"/>
+      <c r="Q101" s="4" t="n">
+        <v>-0.0073</v>
+      </c>
+      <c r="R101" s="5" t="n">
+        <v>-0.74</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -6235,13 +6265,21 @@
       <c r="K102" s="4" t="inlineStr"/>
       <c r="L102" s="4" t="inlineStr"/>
       <c r="M102" s="4" t="inlineStr"/>
-      <c r="N102" s="4" t="inlineStr"/>
-      <c r="O102" s="4" t="inlineStr"/>
+      <c r="N102" s="4" t="n">
+        <v>0.9761</v>
+      </c>
+      <c r="O102" s="4" t="n">
+        <v>0.9875</v>
+      </c>
       <c r="P102" s="4" t="n">
         <v>0.9787</v>
       </c>
-      <c r="Q102" s="4" t="inlineStr"/>
-      <c r="R102" s="5" t="inlineStr"/>
+      <c r="Q102" s="4" t="n">
+        <v>-0.008800000000000001</v>
+      </c>
+      <c r="R102" s="5" t="n">
+        <v>-0.89</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -6642,12 +6680,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>WDBESS1</t>
+          <t>WDBESS2</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Western Downs Battery Energy Storage System</t>
+          <t>Western Downs Battery Energy Storage System (BESS)</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -6656,7 +6694,7 @@
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>272.48</v>
+        <v>269.8</v>
       </c>
       <c r="E110" s="4" t="inlineStr"/>
       <c r="F110" s="4" t="inlineStr"/>
@@ -6668,22 +6706,28 @@
       <c r="L110" s="4" t="inlineStr"/>
       <c r="M110" s="4" t="inlineStr"/>
       <c r="N110" s="4" t="inlineStr"/>
-      <c r="O110" s="4" t="inlineStr"/>
+      <c r="O110" s="4" t="n">
+        <v>0.9899</v>
+      </c>
       <c r="P110" s="4" t="n">
         <v>0.9801</v>
       </c>
-      <c r="Q110" s="4" t="inlineStr"/>
-      <c r="R110" s="5" t="inlineStr"/>
+      <c r="Q110" s="4" t="n">
+        <v>-0.0098</v>
+      </c>
+      <c r="R110" s="5" t="n">
+        <v>-0.99</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>WDBESS2</t>
+          <t>WDBESS1</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Western Downs Battery Energy Storage System (BESS)</t>
+          <t>Western Downs Battery Energy Storage System</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -6692,7 +6736,7 @@
         </is>
       </c>
       <c r="D111" s="3" t="n">
-        <v>269.8</v>
+        <v>272.48</v>
       </c>
       <c r="E111" s="4" t="inlineStr"/>
       <c r="F111" s="4" t="inlineStr"/>
@@ -6703,13 +6747,21 @@
       <c r="K111" s="4" t="inlineStr"/>
       <c r="L111" s="4" t="inlineStr"/>
       <c r="M111" s="4" t="inlineStr"/>
-      <c r="N111" s="4" t="inlineStr"/>
-      <c r="O111" s="4" t="inlineStr"/>
+      <c r="N111" s="4" t="n">
+        <v>0.9762</v>
+      </c>
+      <c r="O111" s="4" t="n">
+        <v>0.9891</v>
+      </c>
       <c r="P111" s="4" t="n">
         <v>0.9801</v>
       </c>
-      <c r="Q111" s="4" t="inlineStr"/>
-      <c r="R111" s="5" t="inlineStr"/>
+      <c r="Q111" s="4" t="n">
+        <v>-0.008999999999999999</v>
+      </c>
+      <c r="R111" s="5" t="n">
+        <v>-0.91</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -7152,60 +7204,66 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>DULAWF1</t>
+          <t>MARYRSF1</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Dulacca Wind Farm</t>
+          <t>Maryrorough Solar Farm</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D120" s="3" t="n">
-        <v>180</v>
+        <v>33</v>
       </c>
       <c r="E120" s="4" t="inlineStr"/>
       <c r="F120" s="4" t="inlineStr"/>
       <c r="G120" s="4" t="inlineStr"/>
       <c r="H120" s="4" t="inlineStr"/>
-      <c r="I120" s="4" t="inlineStr"/>
-      <c r="J120" s="4" t="inlineStr"/>
-      <c r="K120" s="4" t="inlineStr"/>
+      <c r="I120" s="4" t="n">
+        <v>0.9872</v>
+      </c>
+      <c r="J120" s="4" t="n">
+        <v>0.9851</v>
+      </c>
+      <c r="K120" s="4" t="n">
+        <v>0.9789</v>
+      </c>
       <c r="L120" s="4" t="n">
-        <v>0.9540999999999999</v>
+        <v>0.9861</v>
       </c>
       <c r="M120" s="4" t="n">
-        <v>0.9776</v>
+        <v>0.9913999999999999</v>
       </c>
       <c r="N120" s="4" t="n">
-        <v>0.977</v>
+        <v>0.9847</v>
       </c>
       <c r="O120" s="4" t="n">
-        <v>0.9853</v>
+        <v>0.9888</v>
       </c>
       <c r="P120" s="4" t="n">
         <v>0.987</v>
       </c>
       <c r="Q120" s="4" t="n">
-        <v>0.0017</v>
+        <v>-0.0018</v>
       </c>
       <c r="R120" s="5" t="n">
-        <v>0.17</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>MARYRSF1</t>
+          <t>WARWSF1</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Maryrorough Solar Farm</t>
+          <t xml:space="preserve">Warwick Solar Farm 1 </t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -7214,15 +7272,13 @@
         </is>
       </c>
       <c r="D121" s="3" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E121" s="4" t="inlineStr"/>
       <c r="F121" s="4" t="inlineStr"/>
       <c r="G121" s="4" t="inlineStr"/>
       <c r="H121" s="4" t="inlineStr"/>
-      <c r="I121" s="4" t="n">
-        <v>0.9872</v>
-      </c>
+      <c r="I121" s="4" t="inlineStr"/>
       <c r="J121" s="4" t="n">
         <v>0.9851</v>
       </c>
@@ -7254,53 +7310,49 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>WARWSF1</t>
+          <t>DULAWF1</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warwick Solar Farm 1 </t>
+          <t>Dulacca Wind Farm</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D122" s="3" t="n">
-        <v>39</v>
+        <v>180</v>
       </c>
       <c r="E122" s="4" t="inlineStr"/>
       <c r="F122" s="4" t="inlineStr"/>
       <c r="G122" s="4" t="inlineStr"/>
       <c r="H122" s="4" t="inlineStr"/>
       <c r="I122" s="4" t="inlineStr"/>
-      <c r="J122" s="4" t="n">
-        <v>0.9851</v>
-      </c>
-      <c r="K122" s="4" t="n">
-        <v>0.9789</v>
-      </c>
+      <c r="J122" s="4" t="inlineStr"/>
+      <c r="K122" s="4" t="inlineStr"/>
       <c r="L122" s="4" t="n">
-        <v>0.9861</v>
+        <v>0.9540999999999999</v>
       </c>
       <c r="M122" s="4" t="n">
-        <v>0.9913999999999999</v>
+        <v>0.9776</v>
       </c>
       <c r="N122" s="4" t="n">
-        <v>0.9847</v>
+        <v>0.977</v>
       </c>
       <c r="O122" s="4" t="n">
-        <v>0.9888</v>
+        <v>0.9853</v>
       </c>
       <c r="P122" s="4" t="n">
         <v>0.987</v>
       </c>
       <c r="Q122" s="4" t="n">
-        <v>-0.0018</v>
+        <v>0.0017</v>
       </c>
       <c r="R122" s="5" t="n">
-        <v>-0.18</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="123">
@@ -7644,38 +7696,60 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>SNB02</t>
+          <t>DG_QLD1</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Supernode BESS</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>Battery</t>
-        </is>
-      </c>
+          <t>QLD1 Dummy Generator</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr"/>
       <c r="D129" s="3" t="n">
-        <v>337.4</v>
-      </c>
-      <c r="E129" s="4" t="inlineStr"/>
-      <c r="F129" s="4" t="inlineStr"/>
-      <c r="G129" s="4" t="inlineStr"/>
-      <c r="H129" s="4" t="inlineStr"/>
-      <c r="I129" s="4" t="inlineStr"/>
-      <c r="J129" s="4" t="inlineStr"/>
-      <c r="K129" s="4" t="inlineStr"/>
-      <c r="L129" s="4" t="inlineStr"/>
-      <c r="M129" s="4" t="inlineStr"/>
-      <c r="N129" s="4" t="inlineStr"/>
-      <c r="O129" s="4" t="inlineStr"/>
+        <v>3000</v>
+      </c>
+      <c r="E129" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F129" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G129" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H129" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I129" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J129" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K129" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L129" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M129" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N129" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O129" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="P129" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q129" s="4" t="inlineStr"/>
-      <c r="R129" s="5" t="inlineStr"/>
+      <c r="Q129" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R129" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -7705,59 +7779,51 @@
       <c r="K130" s="4" t="inlineStr"/>
       <c r="L130" s="4" t="inlineStr"/>
       <c r="M130" s="4" t="inlineStr"/>
-      <c r="N130" s="4" t="inlineStr"/>
-      <c r="O130" s="4" t="inlineStr"/>
+      <c r="N130" s="4" t="n">
+        <v>0.9877</v>
+      </c>
+      <c r="O130" s="4" t="n">
+        <v>1.0066</v>
+      </c>
       <c r="P130" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q130" s="4" t="inlineStr"/>
-      <c r="R130" s="5" t="inlineStr"/>
+      <c r="Q130" s="4" t="n">
+        <v>-0.0066</v>
+      </c>
+      <c r="R130" s="5" t="n">
+        <v>-0.66</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>DG_QLD1</t>
+          <t>SNB02</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>QLD1 Dummy Generator</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr"/>
+          <t>Supernode BESS</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
       <c r="D131" s="3" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E131" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F131" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G131" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H131" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I131" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J131" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K131" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L131" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M131" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N131" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>337.4</v>
+      </c>
+      <c r="E131" s="4" t="inlineStr"/>
+      <c r="F131" s="4" t="inlineStr"/>
+      <c r="G131" s="4" t="inlineStr"/>
+      <c r="H131" s="4" t="inlineStr"/>
+      <c r="I131" s="4" t="inlineStr"/>
+      <c r="J131" s="4" t="inlineStr"/>
+      <c r="K131" s="4" t="inlineStr"/>
+      <c r="L131" s="4" t="inlineStr"/>
+      <c r="M131" s="4" t="inlineStr"/>
+      <c r="N131" s="4" t="inlineStr"/>
       <c r="O131" s="4" t="n">
         <v>1</v>
       </c>
@@ -7800,12 +7866,18 @@
       <c r="L132" s="4" t="inlineStr"/>
       <c r="M132" s="4" t="inlineStr"/>
       <c r="N132" s="4" t="inlineStr"/>
-      <c r="O132" s="4" t="inlineStr"/>
+      <c r="O132" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="P132" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q132" s="4" t="inlineStr"/>
-      <c r="R132" s="5" t="inlineStr"/>
+      <c r="Q132" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R132" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -7970,12 +8042,18 @@
       <c r="L136" s="4" t="inlineStr"/>
       <c r="M136" s="4" t="inlineStr"/>
       <c r="N136" s="4" t="inlineStr"/>
-      <c r="O136" s="4" t="inlineStr"/>
+      <c r="O136" s="4" t="n">
+        <v>1.0036</v>
+      </c>
       <c r="P136" s="4" t="n">
         <v>1.0015</v>
       </c>
-      <c r="Q136" s="4" t="inlineStr"/>
-      <c r="R136" s="5" t="inlineStr"/>
+      <c r="Q136" s="4" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="R136" s="5" t="n">
+        <v>-0.21</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -8130,12 +8208,18 @@
       <c r="L139" s="4" t="inlineStr"/>
       <c r="M139" s="4" t="inlineStr"/>
       <c r="N139" s="4" t="inlineStr"/>
-      <c r="O139" s="4" t="inlineStr"/>
+      <c r="O139" s="4" t="n">
+        <v>1.0014</v>
+      </c>
       <c r="P139" s="4" t="n">
         <v>1.0027</v>
       </c>
-      <c r="Q139" s="4" t="inlineStr"/>
-      <c r="R139" s="5" t="inlineStr"/>
+      <c r="Q139" s="4" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="R139" s="5" t="n">
+        <v>0.13</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -8223,13 +8307,21 @@
       <c r="K141" s="4" t="inlineStr"/>
       <c r="L141" s="4" t="inlineStr"/>
       <c r="M141" s="4" t="inlineStr"/>
-      <c r="N141" s="4" t="inlineStr"/>
-      <c r="O141" s="4" t="inlineStr"/>
+      <c r="N141" s="4" t="n">
+        <v>1.0033</v>
+      </c>
+      <c r="O141" s="4" t="n">
+        <v>1.0045</v>
+      </c>
       <c r="P141" s="4" t="n">
         <v>1.0035</v>
       </c>
-      <c r="Q141" s="4" t="inlineStr"/>
-      <c r="R141" s="5" t="inlineStr"/>
+      <c r="Q141" s="4" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="R141" s="5" t="n">
+        <v>-0.1</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -8296,12 +8388,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>RPCG</t>
+          <t>STAPYLTON1</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Rocky Point Cogeneration Plant</t>
+          <t>Stapylton Renewable Energy Facility</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -8310,14 +8402,10 @@
         </is>
       </c>
       <c r="D143" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="E143" s="4" t="n">
-        <v>1.0078</v>
-      </c>
-      <c r="F143" s="4" t="n">
-        <v>1.008</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E143" s="4" t="inlineStr"/>
+      <c r="F143" s="4" t="inlineStr"/>
       <c r="G143" s="4" t="n">
         <v>1.0112</v>
       </c>
@@ -8358,12 +8446,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>STAPYLTON1</t>
+          <t>RPCG</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Stapylton Renewable Energy Facility</t>
+          <t>Rocky Point Cogeneration Plant</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -8372,10 +8460,14 @@
         </is>
       </c>
       <c r="D144" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E144" s="4" t="inlineStr"/>
-      <c r="F144" s="4" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="E144" s="4" t="n">
+        <v>1.0078</v>
+      </c>
+      <c r="F144" s="4" t="n">
+        <v>1.008</v>
+      </c>
       <c r="G144" s="4" t="n">
         <v>1.0112</v>
       </c>
@@ -8830,12 +8922,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>EDLRGNRD</t>
+          <t>ROCHEDAL</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Roghan Road LFG Power Plant</t>
+          <t>Rochedale Renewable Energy Facility</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -8844,22 +8936,22 @@
         </is>
       </c>
       <c r="D153" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E153" s="4" t="n">
-        <v>1.0057</v>
+        <v>1.0067</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>1.0049</v>
+        <v>1.0091</v>
       </c>
       <c r="G153" s="4" t="n">
-        <v>1.0044</v>
+        <v>1.0114</v>
       </c>
       <c r="H153" s="4" t="n">
-        <v>1.0042</v>
+        <v>1.0123</v>
       </c>
       <c r="I153" s="4" t="n">
-        <v>1.0042</v>
+        <v>1.0121</v>
       </c>
       <c r="J153" s="4" t="inlineStr"/>
       <c r="K153" s="4" t="inlineStr"/>
@@ -8874,12 +8966,12 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>ROCHEDAL</t>
+          <t>WHIT1</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Rochedale Renewable Energy Facility</t>
+          <t>Whitwood Road Renewable Energy Facility</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -8888,22 +8980,22 @@
         </is>
       </c>
       <c r="D154" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E154" s="4" t="n">
-        <v>1.0067</v>
+        <v>0.9953</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>1.0091</v>
+        <v>0.9968</v>
       </c>
       <c r="G154" s="4" t="n">
-        <v>1.0114</v>
+        <v>0.9999</v>
       </c>
       <c r="H154" s="4" t="n">
-        <v>1.0123</v>
+        <v>1.0001</v>
       </c>
       <c r="I154" s="4" t="n">
-        <v>1.0121</v>
+        <v>1.0006</v>
       </c>
       <c r="J154" s="4" t="inlineStr"/>
       <c r="K154" s="4" t="inlineStr"/>
@@ -8918,12 +9010,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>WHIT1</t>
+          <t>EDLRGNRD</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Whitwood Road Renewable Energy Facility</t>
+          <t>Roghan Road LFG Power Plant</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -8932,22 +9024,22 @@
         </is>
       </c>
       <c r="D155" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E155" s="4" t="n">
-        <v>0.9953</v>
+        <v>1.0057</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>0.9968</v>
+        <v>1.0049</v>
       </c>
       <c r="G155" s="4" t="n">
-        <v>0.9999</v>
+        <v>1.0044</v>
       </c>
       <c r="H155" s="4" t="n">
-        <v>1.0001</v>
+        <v>1.0042</v>
       </c>
       <c r="I155" s="4" t="n">
-        <v>1.0006</v>
+        <v>1.0042</v>
       </c>
       <c r="J155" s="4" t="inlineStr"/>
       <c r="K155" s="4" t="inlineStr"/>
@@ -9102,12 +9194,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>WDBESSG1</t>
+          <t>WANDBG1</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Western Downs Battery Energy Storage System (BESS)</t>
+          <t>Wandoan BESS</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -9116,7 +9208,7 @@
         </is>
       </c>
       <c r="D159" s="3" t="n">
-        <v>272</v>
+        <v>123</v>
       </c>
       <c r="E159" s="4" t="inlineStr"/>
       <c r="F159" s="4" t="inlineStr"/>
@@ -9124,13 +9216,17 @@
       <c r="H159" s="4" t="inlineStr"/>
       <c r="I159" s="4" t="inlineStr"/>
       <c r="J159" s="4" t="inlineStr"/>
-      <c r="K159" s="4" t="inlineStr"/>
-      <c r="L159" s="4" t="inlineStr"/>
+      <c r="K159" s="4" t="n">
+        <v>0.9764</v>
+      </c>
+      <c r="L159" s="4" t="n">
+        <v>0.9767</v>
+      </c>
       <c r="M159" s="4" t="n">
-        <v>0.9586</v>
+        <v>0.9751</v>
       </c>
       <c r="N159" s="4" t="n">
-        <v>0.9556</v>
+        <v>0.9823</v>
       </c>
       <c r="O159" s="4" t="inlineStr"/>
       <c r="P159" s="4" t="inlineStr"/>
@@ -9140,12 +9236,12 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>CHBESSG1</t>
+          <t>WDBESSG1</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Chinchilla BESS</t>
+          <t>Western Downs Battery Energy Storage System (BESS)</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -9154,7 +9250,7 @@
         </is>
       </c>
       <c r="D160" s="3" t="n">
-        <v>134</v>
+        <v>272</v>
       </c>
       <c r="E160" s="4" t="inlineStr"/>
       <c r="F160" s="4" t="inlineStr"/>
@@ -9165,10 +9261,10 @@
       <c r="K160" s="4" t="inlineStr"/>
       <c r="L160" s="4" t="inlineStr"/>
       <c r="M160" s="4" t="n">
-        <v>0.9588</v>
+        <v>0.9586</v>
       </c>
       <c r="N160" s="4" t="n">
-        <v>0.9611</v>
+        <v>0.9556</v>
       </c>
       <c r="O160" s="4" t="inlineStr"/>
       <c r="P160" s="4" t="inlineStr"/>
@@ -9178,12 +9274,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>WANDBG1</t>
+          <t>CHBESSG1</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Wandoan BESS</t>
+          <t>Chinchilla BESS</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -9192,7 +9288,7 @@
         </is>
       </c>
       <c r="D161" s="3" t="n">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="E161" s="4" t="inlineStr"/>
       <c r="F161" s="4" t="inlineStr"/>
@@ -9200,17 +9296,13 @@
       <c r="H161" s="4" t="inlineStr"/>
       <c r="I161" s="4" t="inlineStr"/>
       <c r="J161" s="4" t="inlineStr"/>
-      <c r="K161" s="4" t="n">
-        <v>0.9764</v>
-      </c>
-      <c r="L161" s="4" t="n">
-        <v>0.9767</v>
-      </c>
+      <c r="K161" s="4" t="inlineStr"/>
+      <c r="L161" s="4" t="inlineStr"/>
       <c r="M161" s="4" t="n">
-        <v>0.9751</v>
+        <v>0.9588</v>
       </c>
       <c r="N161" s="4" t="n">
-        <v>0.9823</v>
+        <v>0.9611</v>
       </c>
       <c r="O161" s="4" t="inlineStr"/>
       <c r="P161" s="4" t="inlineStr"/>
@@ -9652,13 +9744,13 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>KSP1</t>
+          <t>HUGSF1</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr"/>
       <c r="C10" s="4" t="inlineStr"/>
       <c r="D10" s="4" t="n">
-        <v>1.0149</v>
+        <v>1.0115</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>0.8842</v>
@@ -9730,13 +9822,13 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>HUGSF1</t>
+          <t>KSP1</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr"/>
       <c r="C12" s="4" t="inlineStr"/>
       <c r="D12" s="4" t="n">
-        <v>1.0115</v>
+        <v>1.0149</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>0.8842</v>
@@ -9868,16 +9960,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>LRSF1</t>
+          <t>CLERMSF1</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr"/>
       <c r="C16" s="4" t="inlineStr"/>
-      <c r="D16" s="4" t="n">
-        <v>0.9689</v>
-      </c>
+      <c r="D16" s="4" t="inlineStr"/>
       <c r="E16" s="4" t="n">
-        <v>0.8934</v>
+        <v>0.8862</v>
       </c>
       <c r="F16" s="4" t="n">
         <v>0.8735000000000001</v>
@@ -9948,14 +10038,16 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>CLERMSF1</t>
+          <t>LRSF1</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr"/>
       <c r="C18" s="4" t="inlineStr"/>
-      <c r="D18" s="4" t="inlineStr"/>
+      <c r="D18" s="4" t="n">
+        <v>0.9689</v>
+      </c>
       <c r="E18" s="4" t="n">
-        <v>0.8862</v>
+        <v>0.8934</v>
       </c>
       <c r="F18" s="4" t="n">
         <v>0.8735000000000001</v>
@@ -10105,8 +10197,12 @@
       <c r="H23" s="4" t="inlineStr"/>
       <c r="I23" s="4" t="inlineStr"/>
       <c r="J23" s="4" t="inlineStr"/>
-      <c r="K23" s="4" t="inlineStr"/>
-      <c r="L23" s="4" t="inlineStr"/>
+      <c r="K23" s="4" t="n">
+        <v>0.9528</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>0.9358</v>
+      </c>
       <c r="M23" s="4" t="n">
         <v>0.9008</v>
       </c>
@@ -10329,7 +10425,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>OAKY2</t>
+          <t>OAKYCREK</t>
         </is>
       </c>
       <c r="B29" s="4" t="n">
@@ -10372,7 +10468,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>OAKYCREK</t>
+          <t>OAKY2</t>
         </is>
       </c>
       <c r="B30" s="4" t="n">
@@ -10415,7 +10511,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>CALL_A_4</t>
+          <t>CALLNL4</t>
         </is>
       </c>
       <c r="B31" s="4" t="n">
@@ -10450,7 +10546,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>CALLNL4</t>
+          <t>CALL_A_4</t>
         </is>
       </c>
       <c r="B32" s="4" t="n">
@@ -10485,7 +10581,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>STAN-3</t>
+          <t>STAN-1</t>
         </is>
       </c>
       <c r="B33" s="4" t="n">
@@ -10571,7 +10667,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>STAN-1</t>
+          <t>STAN-3</t>
         </is>
       </c>
       <c r="B35" s="4" t="n">
@@ -10829,7 +10925,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>BRDDSF01</t>
+          <t>BRDDBES1</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr"/>
@@ -10852,7 +10948,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>BRDDBES1</t>
+          <t>BRDDSF01</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr"/>
@@ -10865,7 +10961,9 @@
       <c r="I42" s="4" t="inlineStr"/>
       <c r="J42" s="4" t="inlineStr"/>
       <c r="K42" s="4" t="inlineStr"/>
-      <c r="L42" s="4" t="inlineStr"/>
+      <c r="L42" s="4" t="n">
+        <v>0.929</v>
+      </c>
       <c r="M42" s="4" t="n">
         <v>0.9247</v>
       </c>
@@ -11045,7 +11143,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GSTONE6</t>
+          <t>GSTONE5</t>
         </is>
       </c>
       <c r="B47" s="4" t="n">
@@ -11088,7 +11186,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GSTONE5</t>
+          <t>GSTONE6</t>
         </is>
       </c>
       <c r="B48" s="4" t="n">
@@ -11510,7 +11608,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>SRSF1</t>
+          <t>CHILDSF1</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr"/>
@@ -11547,7 +11645,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>CHILDSF1</t>
+          <t>SRSF1</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr"/>
@@ -11627,7 +11725,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>MSTUART3</t>
+          <t>MSTUART2</t>
         </is>
       </c>
       <c r="B63" s="4" t="n">
@@ -11670,7 +11768,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>MSTUART2</t>
+          <t>MSTUART3</t>
         </is>
       </c>
       <c r="B64" s="4" t="n">
@@ -11887,7 +11985,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>KAREEYA4</t>
+          <t>KAREEYA2</t>
         </is>
       </c>
       <c r="B71" s="4" t="n">
@@ -11930,7 +12028,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>KAREEYA1</t>
+          <t>KAREEYA5</t>
         </is>
       </c>
       <c r="B72" s="4" t="n">
@@ -11973,7 +12071,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>KAREEYA2</t>
+          <t>KAREEYA4</t>
         </is>
       </c>
       <c r="B73" s="4" t="n">
@@ -12059,7 +12157,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>KAREEYA5</t>
+          <t>KAREEYA1</t>
         </is>
       </c>
       <c r="B75" s="4" t="n">
@@ -12293,7 +12391,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>BRAEMAR6</t>
+          <t>BRAEMAR2</t>
         </is>
       </c>
       <c r="B81" s="4" t="n">
@@ -12379,7 +12477,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>BRAEMAR1</t>
+          <t>BRAEMAR7</t>
         </is>
       </c>
       <c r="B83" s="4" t="n">
@@ -12422,7 +12520,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>BRAEMAR2</t>
+          <t>BRAEMAR6</t>
         </is>
       </c>
       <c r="B84" s="4" t="n">
@@ -12465,7 +12563,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>BRAEMAR7</t>
+          <t>BRAEMAR1</t>
         </is>
       </c>
       <c r="B85" s="4" t="n">
@@ -12662,7 +12760,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>TARONG#4</t>
+          <t>TARONG#3</t>
         </is>
       </c>
       <c r="B90" s="4" t="n">
@@ -12705,7 +12803,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>TARONG#3</t>
+          <t>TARONG#4</t>
         </is>
       </c>
       <c r="B91" s="4" t="n">
@@ -12963,8 +13061,12 @@
       <c r="H97" s="4" t="inlineStr"/>
       <c r="I97" s="4" t="inlineStr"/>
       <c r="J97" s="4" t="inlineStr"/>
-      <c r="K97" s="4" t="inlineStr"/>
-      <c r="L97" s="4" t="inlineStr"/>
+      <c r="K97" s="4" t="n">
+        <v>0.9837</v>
+      </c>
+      <c r="L97" s="4" t="n">
+        <v>0.9836</v>
+      </c>
       <c r="M97" s="4" t="n">
         <v>0.9772999999999999</v>
       </c>
@@ -13015,7 +13117,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>ROMA_7</t>
+          <t>ROMA_8</t>
         </is>
       </c>
       <c r="B99" s="4" t="n">
@@ -13058,7 +13160,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>ROMA_8</t>
+          <t>ROMA_7</t>
         </is>
       </c>
       <c r="B100" s="4" t="n">
@@ -13113,8 +13215,12 @@
       <c r="H101" s="4" t="inlineStr"/>
       <c r="I101" s="4" t="inlineStr"/>
       <c r="J101" s="4" t="inlineStr"/>
-      <c r="K101" s="4" t="inlineStr"/>
-      <c r="L101" s="4" t="inlineStr"/>
+      <c r="K101" s="4" t="n">
+        <v>0.9698</v>
+      </c>
+      <c r="L101" s="4" t="n">
+        <v>0.9851</v>
+      </c>
       <c r="M101" s="4" t="n">
         <v>0.9778</v>
       </c>
@@ -13134,8 +13240,12 @@
       <c r="H102" s="4" t="inlineStr"/>
       <c r="I102" s="4" t="inlineStr"/>
       <c r="J102" s="4" t="inlineStr"/>
-      <c r="K102" s="4" t="inlineStr"/>
-      <c r="L102" s="4" t="inlineStr"/>
+      <c r="K102" s="4" t="n">
+        <v>0.9761</v>
+      </c>
+      <c r="L102" s="4" t="n">
+        <v>0.9875</v>
+      </c>
       <c r="M102" s="4" t="n">
         <v>0.9787</v>
       </c>
@@ -13406,7 +13516,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>WDBESS1</t>
+          <t>WDBESS2</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr"/>
@@ -13419,7 +13529,9 @@
       <c r="I110" s="4" t="inlineStr"/>
       <c r="J110" s="4" t="inlineStr"/>
       <c r="K110" s="4" t="inlineStr"/>
-      <c r="L110" s="4" t="inlineStr"/>
+      <c r="L110" s="4" t="n">
+        <v>0.9899</v>
+      </c>
       <c r="M110" s="4" t="n">
         <v>0.9801</v>
       </c>
@@ -13427,7 +13539,7 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>WDBESS2</t>
+          <t>WDBESS1</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr"/>
@@ -13439,8 +13551,12 @@
       <c r="H111" s="4" t="inlineStr"/>
       <c r="I111" s="4" t="inlineStr"/>
       <c r="J111" s="4" t="inlineStr"/>
-      <c r="K111" s="4" t="inlineStr"/>
-      <c r="L111" s="4" t="inlineStr"/>
+      <c r="K111" s="4" t="n">
+        <v>0.9762</v>
+      </c>
+      <c r="L111" s="4" t="n">
+        <v>0.9891</v>
+      </c>
       <c r="M111" s="4" t="n">
         <v>0.9801</v>
       </c>
@@ -13734,27 +13850,33 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>DULAWF1</t>
+          <t>MARYRSF1</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr"/>
       <c r="C120" s="4" t="inlineStr"/>
       <c r="D120" s="4" t="inlineStr"/>
       <c r="E120" s="4" t="inlineStr"/>
-      <c r="F120" s="4" t="inlineStr"/>
-      <c r="G120" s="4" t="inlineStr"/>
-      <c r="H120" s="4" t="inlineStr"/>
+      <c r="F120" s="4" t="n">
+        <v>0.9872</v>
+      </c>
+      <c r="G120" s="4" t="n">
+        <v>0.9851</v>
+      </c>
+      <c r="H120" s="4" t="n">
+        <v>0.9789</v>
+      </c>
       <c r="I120" s="4" t="n">
-        <v>0.9540999999999999</v>
+        <v>0.9861</v>
       </c>
       <c r="J120" s="4" t="n">
-        <v>0.9776</v>
+        <v>0.9913999999999999</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>0.977</v>
+        <v>0.9847</v>
       </c>
       <c r="L120" s="4" t="n">
-        <v>0.9853</v>
+        <v>0.9888</v>
       </c>
       <c r="M120" s="4" t="n">
         <v>0.987</v>
@@ -13763,16 +13885,14 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>MARYRSF1</t>
+          <t>WARWSF1</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr"/>
       <c r="C121" s="4" t="inlineStr"/>
       <c r="D121" s="4" t="inlineStr"/>
       <c r="E121" s="4" t="inlineStr"/>
-      <c r="F121" s="4" t="n">
-        <v>0.9872</v>
-      </c>
+      <c r="F121" s="4" t="inlineStr"/>
       <c r="G121" s="4" t="n">
         <v>0.9851</v>
       </c>
@@ -13798,7 +13918,7 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>WARWSF1</t>
+          <t>DULAWF1</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr"/>
@@ -13806,23 +13926,19 @@
       <c r="D122" s="4" t="inlineStr"/>
       <c r="E122" s="4" t="inlineStr"/>
       <c r="F122" s="4" t="inlineStr"/>
-      <c r="G122" s="4" t="n">
-        <v>0.9851</v>
-      </c>
-      <c r="H122" s="4" t="n">
-        <v>0.9789</v>
-      </c>
+      <c r="G122" s="4" t="inlineStr"/>
+      <c r="H122" s="4" t="inlineStr"/>
       <c r="I122" s="4" t="n">
-        <v>0.9861</v>
+        <v>0.9540999999999999</v>
       </c>
       <c r="J122" s="4" t="n">
-        <v>0.9913999999999999</v>
+        <v>0.9776</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>0.9847</v>
+        <v>0.977</v>
       </c>
       <c r="L122" s="4" t="n">
-        <v>0.9888</v>
+        <v>0.9853</v>
       </c>
       <c r="M122" s="4" t="n">
         <v>0.987</v>
@@ -14055,20 +14171,42 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>SNB02</t>
-        </is>
-      </c>
-      <c r="B129" s="4" t="inlineStr"/>
-      <c r="C129" s="4" t="inlineStr"/>
-      <c r="D129" s="4" t="inlineStr"/>
-      <c r="E129" s="4" t="inlineStr"/>
-      <c r="F129" s="4" t="inlineStr"/>
-      <c r="G129" s="4" t="inlineStr"/>
-      <c r="H129" s="4" t="inlineStr"/>
-      <c r="I129" s="4" t="inlineStr"/>
-      <c r="J129" s="4" t="inlineStr"/>
-      <c r="K129" s="4" t="inlineStr"/>
-      <c r="L129" s="4" t="inlineStr"/>
+          <t>DG_QLD1</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C129" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D129" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F129" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G129" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H129" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I129" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J129" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K129" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L129" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="M129" s="4" t="n">
         <v>1</v>
       </c>
@@ -14088,8 +14226,12 @@
       <c r="H130" s="4" t="inlineStr"/>
       <c r="I130" s="4" t="inlineStr"/>
       <c r="J130" s="4" t="inlineStr"/>
-      <c r="K130" s="4" t="inlineStr"/>
-      <c r="L130" s="4" t="inlineStr"/>
+      <c r="K130" s="4" t="n">
+        <v>0.9877</v>
+      </c>
+      <c r="L130" s="4" t="n">
+        <v>1.0066</v>
+      </c>
       <c r="M130" s="4" t="n">
         <v>1</v>
       </c>
@@ -14097,39 +14239,19 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>DG_QLD1</t>
-        </is>
-      </c>
-      <c r="B131" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C131" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D131" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E131" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F131" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G131" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H131" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I131" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J131" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K131" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>SNB02</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr"/>
+      <c r="C131" s="4" t="inlineStr"/>
+      <c r="D131" s="4" t="inlineStr"/>
+      <c r="E131" s="4" t="inlineStr"/>
+      <c r="F131" s="4" t="inlineStr"/>
+      <c r="G131" s="4" t="inlineStr"/>
+      <c r="H131" s="4" t="inlineStr"/>
+      <c r="I131" s="4" t="inlineStr"/>
+      <c r="J131" s="4" t="inlineStr"/>
+      <c r="K131" s="4" t="inlineStr"/>
       <c r="L131" s="4" t="n">
         <v>1</v>
       </c>
@@ -14153,7 +14275,9 @@
       <c r="I132" s="4" t="inlineStr"/>
       <c r="J132" s="4" t="inlineStr"/>
       <c r="K132" s="4" t="inlineStr"/>
-      <c r="L132" s="4" t="inlineStr"/>
+      <c r="L132" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="M132" s="4" t="n">
         <v>1</v>
       </c>
@@ -14259,7 +14383,9 @@
       <c r="I136" s="4" t="inlineStr"/>
       <c r="J136" s="4" t="inlineStr"/>
       <c r="K136" s="4" t="inlineStr"/>
-      <c r="L136" s="4" t="inlineStr"/>
+      <c r="L136" s="4" t="n">
+        <v>1.0036</v>
+      </c>
       <c r="M136" s="4" t="n">
         <v>1.0015</v>
       </c>
@@ -14366,7 +14492,9 @@
       <c r="I139" s="4" t="inlineStr"/>
       <c r="J139" s="4" t="inlineStr"/>
       <c r="K139" s="4" t="inlineStr"/>
-      <c r="L139" s="4" t="inlineStr"/>
+      <c r="L139" s="4" t="n">
+        <v>1.0014</v>
+      </c>
       <c r="M139" s="4" t="n">
         <v>1.0027</v>
       </c>
@@ -14429,8 +14557,12 @@
       <c r="H141" s="4" t="inlineStr"/>
       <c r="I141" s="4" t="inlineStr"/>
       <c r="J141" s="4" t="inlineStr"/>
-      <c r="K141" s="4" t="inlineStr"/>
-      <c r="L141" s="4" t="inlineStr"/>
+      <c r="K141" s="4" t="n">
+        <v>1.0033</v>
+      </c>
+      <c r="L141" s="4" t="n">
+        <v>1.0045</v>
+      </c>
       <c r="M141" s="4" t="n">
         <v>1.0035</v>
       </c>
@@ -14481,15 +14613,11 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>RPCG</t>
-        </is>
-      </c>
-      <c r="B143" s="4" t="n">
-        <v>1.0078</v>
-      </c>
-      <c r="C143" s="4" t="n">
-        <v>1.008</v>
-      </c>
+          <t>STAPYLTON1</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="inlineStr"/>
+      <c r="C143" s="4" t="inlineStr"/>
       <c r="D143" s="4" t="n">
         <v>1.0112</v>
       </c>
@@ -14524,11 +14652,15 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>STAPYLTON1</t>
-        </is>
-      </c>
-      <c r="B144" s="4" t="inlineStr"/>
-      <c r="C144" s="4" t="inlineStr"/>
+          <t>RPCG</t>
+        </is>
+      </c>
+      <c r="B144" s="4" t="n">
+        <v>1.0078</v>
+      </c>
+      <c r="C144" s="4" t="n">
+        <v>1.008</v>
+      </c>
       <c r="D144" s="4" t="n">
         <v>1.0112</v>
       </c>
@@ -14837,23 +14969,23 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>EDLRGNRD</t>
+          <t>ROCHEDAL</t>
         </is>
       </c>
       <c r="B153" s="4" t="n">
-        <v>1.0057</v>
+        <v>1.0067</v>
       </c>
       <c r="C153" s="4" t="n">
-        <v>1.0049</v>
+        <v>1.0091</v>
       </c>
       <c r="D153" s="4" t="n">
-        <v>1.0044</v>
+        <v>1.0114</v>
       </c>
       <c r="E153" s="4" t="n">
-        <v>1.0042</v>
+        <v>1.0123</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>1.0042</v>
+        <v>1.0121</v>
       </c>
       <c r="G153" s="4" t="inlineStr"/>
       <c r="H153" s="4" t="inlineStr"/>
@@ -14866,23 +14998,23 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>ROCHEDAL</t>
+          <t>WHIT1</t>
         </is>
       </c>
       <c r="B154" s="4" t="n">
-        <v>1.0067</v>
+        <v>0.9953</v>
       </c>
       <c r="C154" s="4" t="n">
-        <v>1.0091</v>
+        <v>0.9968</v>
       </c>
       <c r="D154" s="4" t="n">
-        <v>1.0114</v>
+        <v>0.9999</v>
       </c>
       <c r="E154" s="4" t="n">
-        <v>1.0123</v>
+        <v>1.0001</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>1.0121</v>
+        <v>1.0006</v>
       </c>
       <c r="G154" s="4" t="inlineStr"/>
       <c r="H154" s="4" t="inlineStr"/>
@@ -14895,23 +15027,23 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>WHIT1</t>
+          <t>EDLRGNRD</t>
         </is>
       </c>
       <c r="B155" s="4" t="n">
-        <v>0.9953</v>
+        <v>1.0057</v>
       </c>
       <c r="C155" s="4" t="n">
-        <v>0.9968</v>
+        <v>1.0049</v>
       </c>
       <c r="D155" s="4" t="n">
-        <v>0.9999</v>
+        <v>1.0044</v>
       </c>
       <c r="E155" s="4" t="n">
-        <v>1.0001</v>
+        <v>1.0042</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>1.0006</v>
+        <v>1.0042</v>
       </c>
       <c r="G155" s="4" t="inlineStr"/>
       <c r="H155" s="4" t="inlineStr"/>
@@ -15025,7 +15157,7 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>WDBESSG1</t>
+          <t>WANDBG1</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr"/>
@@ -15034,13 +15166,17 @@
       <c r="E159" s="4" t="inlineStr"/>
       <c r="F159" s="4" t="inlineStr"/>
       <c r="G159" s="4" t="inlineStr"/>
-      <c r="H159" s="4" t="inlineStr"/>
-      <c r="I159" s="4" t="inlineStr"/>
+      <c r="H159" s="4" t="n">
+        <v>0.9764</v>
+      </c>
+      <c r="I159" s="4" t="n">
+        <v>0.9767</v>
+      </c>
       <c r="J159" s="4" t="n">
-        <v>0.9586</v>
+        <v>0.9751</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>0.9556</v>
+        <v>0.9823</v>
       </c>
       <c r="L159" s="4" t="inlineStr"/>
       <c r="M159" s="4" t="inlineStr"/>
@@ -15048,7 +15184,7 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>CHBESSG1</t>
+          <t>WDBESSG1</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr"/>
@@ -15060,10 +15196,10 @@
       <c r="H160" s="4" t="inlineStr"/>
       <c r="I160" s="4" t="inlineStr"/>
       <c r="J160" s="4" t="n">
-        <v>0.9588</v>
+        <v>0.9586</v>
       </c>
       <c r="K160" s="4" t="n">
-        <v>0.9611</v>
+        <v>0.9556</v>
       </c>
       <c r="L160" s="4" t="inlineStr"/>
       <c r="M160" s="4" t="inlineStr"/>
@@ -15071,7 +15207,7 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>WANDBG1</t>
+          <t>CHBESSG1</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr"/>
@@ -15080,17 +15216,13 @@
       <c r="E161" s="4" t="inlineStr"/>
       <c r="F161" s="4" t="inlineStr"/>
       <c r="G161" s="4" t="inlineStr"/>
-      <c r="H161" s="4" t="n">
-        <v>0.9764</v>
-      </c>
-      <c r="I161" s="4" t="n">
-        <v>0.9767</v>
-      </c>
+      <c r="H161" s="4" t="inlineStr"/>
+      <c r="I161" s="4" t="inlineStr"/>
       <c r="J161" s="4" t="n">
-        <v>0.9751</v>
+        <v>0.9588</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>0.9823</v>
+        <v>0.9611</v>
       </c>
       <c r="L161" s="4" t="inlineStr"/>
       <c r="M161" s="4" t="inlineStr"/>
@@ -15477,12 +15609,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>HUGSF1</t>
+          <t>KSP1</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Hughenden Solar Farm</t>
+          <t>Kidston Solar Project Phase One</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -15506,12 +15638,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>KSP1</t>
+          <t>HUGSF1</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Kidston Solar Project Phase One</t>
+          <t>Hughenden Solar Farm</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -15767,12 +15899,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>LRSF1</t>
+          <t>CLERMSF1</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Longreach Solar Farm</t>
+          <t>Clermont Solar Farm</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -15796,12 +15928,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>CLERMSF1</t>
+          <t>LRSF1</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Clermont Solar Farm</t>
+          <t>Longreach Solar Farm</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -15985,7 +16117,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>MSTUART3</t>
+          <t>MSTUART2</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -16014,7 +16146,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>MSTUART2</t>
+          <t>MSTUART3</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -16159,7 +16291,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>ROMA_7</t>
+          <t>ROMA_8</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -16188,7 +16320,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>ROMA_8</t>
+          <t>ROMA_7</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -16246,12 +16378,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>BRAEMAR2</t>
+          <t>BRAEMAR6</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Braemar Power Station</t>
+          <t>Braemar 2 Power Station</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -16275,12 +16407,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>BRAEMAR1</t>
+          <t>BRAEMAR7</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Braemar Power Station</t>
+          <t>Braemar 2 Power Station</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -16304,12 +16436,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>BRAEMAR7</t>
+          <t>BRAEMAR1</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Braemar 2 Power Station</t>
+          <t>Braemar Power Station</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -16333,12 +16465,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>BRAEMAR6</t>
+          <t>BRAEMAR2</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Braemar 2 Power Station</t>
+          <t>Braemar Power Station</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -16507,12 +16639,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>RPCG</t>
+          <t>STAPYLTON1</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Rocky Point Cogeneration Plant</t>
+          <t>Stapylton Renewable Energy Facility</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">

--- a/outputs/QLD_mlf.xlsx
+++ b/outputs/QLD_mlf.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MLF Table" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Biggest Movers" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="MLF Table" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Biggest Movers" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -859,12 +859,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>DAYDSF1</t>
+          <t>HAYMSF1</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Daydream Solar Farm</t>
+          <t>Hayman Solar Farm</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>167</v>
+        <v>57.75</v>
       </c>
       <c r="E6" s="5" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr"/>
@@ -920,12 +920,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>HAYMSF1</t>
+          <t>DAYDSF1</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Hayman Solar Farm</t>
+          <t>Daydream Solar Farm</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>57.75</v>
+        <v>167</v>
       </c>
       <c r="E7" s="5" t="inlineStr"/>
       <c r="F7" s="5" t="inlineStr"/>
@@ -1103,12 +1103,12 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>HUGSF1</t>
+          <t>KSP1</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Hughenden Solar Farm</t>
+          <t>Kidston Solar Project Phase One</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -1117,12 +1117,12 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>20.97</v>
+        <v>50</v>
       </c>
       <c r="E10" s="5" t="inlineStr"/>
       <c r="F10" s="5" t="inlineStr"/>
       <c r="G10" s="5" t="n">
-        <v>1.0115</v>
+        <v>1.0149</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>0.8842</v>
@@ -1229,12 +1229,12 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>KSP1</t>
+          <t>HUGSF1</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Kidston Solar Project Phase One</t>
+          <t>Hughenden Solar Farm</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1243,12 +1243,12 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>50</v>
+        <v>20.97</v>
       </c>
       <c r="E12" s="5" t="inlineStr"/>
       <c r="F12" s="5" t="inlineStr"/>
       <c r="G12" s="5" t="n">
-        <v>1.0149</v>
+        <v>1.0115</v>
       </c>
       <c r="H12" s="5" t="n">
         <v>0.8842</v>
@@ -1345,12 +1345,12 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>MIDDLSF1</t>
+          <t>EMERASF1</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Middlemount Solar Farm</t>
+          <t>Emerald Solar Park</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1359,15 +1359,19 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="E14" s="5" t="inlineStr"/>
       <c r="F14" s="5" t="inlineStr"/>
       <c r="G14" s="5" t="inlineStr"/>
-      <c r="H14" s="5" t="inlineStr"/>
-      <c r="I14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="n">
+        <v>0.8778</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>0.8712</v>
+      </c>
       <c r="J14" s="5" t="n">
-        <v>0.882</v>
+        <v>0.8864</v>
       </c>
       <c r="K14" s="5" t="n">
         <v>0.9237</v>
@@ -1402,12 +1406,12 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>EMERASF1</t>
+          <t>MIDDLSF1</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Emerald Solar Park</t>
+          <t>Middlemount Solar Farm</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1416,19 +1420,15 @@
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>88</v>
+        <v>30</v>
       </c>
       <c r="E15" s="5" t="inlineStr"/>
       <c r="F15" s="5" t="inlineStr"/>
       <c r="G15" s="5" t="inlineStr"/>
-      <c r="H15" s="5" t="n">
-        <v>0.8778</v>
-      </c>
-      <c r="I15" s="5" t="n">
-        <v>0.8712</v>
-      </c>
+      <c r="H15" s="5" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr"/>
       <c r="J15" s="5" t="n">
-        <v>0.8864</v>
+        <v>0.882</v>
       </c>
       <c r="K15" s="5" t="n">
         <v>0.9237</v>
@@ -1524,12 +1524,12 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>BARCSF1</t>
+          <t>LRSF1</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Barcaldine Solar Farm</t>
+          <t>Longreach Solar Farm</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1538,14 +1538,12 @@
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="n">
-        <v>0.9385</v>
-      </c>
+      <c r="F17" s="5" t="inlineStr"/>
       <c r="G17" s="5" t="n">
-        <v>0.9715</v>
+        <v>0.9689</v>
       </c>
       <c r="H17" s="5" t="n">
         <v>0.8934</v>
@@ -1589,12 +1587,12 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>LRSF1</t>
+          <t>BARCSF1</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Longreach Solar Farm</t>
+          <t>Barcaldine Solar Farm</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -1603,12 +1601,14 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="n">
+        <v>0.9385</v>
+      </c>
       <c r="G18" s="5" t="n">
-        <v>0.9689</v>
+        <v>0.9715</v>
       </c>
       <c r="H18" s="5" t="n">
         <v>0.8934</v>
@@ -1713,7 +1713,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>KIDSPHG2</t>
+          <t>KIDSPHG1</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1760,7 +1760,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>KIDSPHG1</t>
+          <t>KIDSPHG2</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1856,7 +1856,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>CALL_B_2</t>
+          <t>CALL_B_1</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1923,7 +1923,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>CALL_B_1</t>
+          <t>CALL_B_2</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -2191,12 +2191,12 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>OAKY2</t>
+          <t>OAKYCREK</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Oaky Creek 2</t>
+          <t>Oaky Creek Power Station</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -2205,7 +2205,7 @@
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E28" s="5" t="n">
         <v>1.0373</v>
@@ -2258,12 +2258,12 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>OAKYCREK</t>
+          <t>OAKY2</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Oaky Creek Power Station</t>
+          <t>Oaky Creek 2</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -2272,7 +2272,7 @@
         </is>
       </c>
       <c r="D29" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>1.0373</v>
@@ -2325,7 +2325,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>CALLNL4</t>
+          <t>CALL_A_4</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -2333,7 +2333,11 @@
           <t>Callide Power Station</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr"/>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
       <c r="D30" s="4" t="n">
         <v>30</v>
       </c>
@@ -2376,7 +2380,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>CALL_A_4</t>
+          <t>CALLNL4</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -2384,11 +2388,7 @@
           <t>Callide Power Station</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>Fossil</t>
-        </is>
-      </c>
+      <c r="C31" s="3" t="inlineStr"/>
       <c r="D31" s="4" t="n">
         <v>30</v>
       </c>
@@ -2498,7 +2498,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>STAN-3</t>
+          <t>STAN-1</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>STAN-4</t>
+          <t>STAN-3</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -2632,7 +2632,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>STAN-1</t>
+          <t>STAN-4</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -2967,7 +2967,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>BRDDBES1</t>
+          <t>BRDDSF01</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -2977,11 +2977,11 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>240</v>
+        <v>368</v>
       </c>
       <c r="E40" s="5" t="inlineStr"/>
       <c r="F40" s="5" t="inlineStr"/>
@@ -2997,32 +2997,24 @@
       <c r="P40" s="5" t="n">
         <v>0.929</v>
       </c>
-      <c r="Q40" s="5" t="n">
-        <v>0.929</v>
-      </c>
+      <c r="Q40" s="5" t="inlineStr"/>
       <c r="R40" s="5" t="n">
         <v>0.9247</v>
       </c>
-      <c r="S40" s="5" t="n">
-        <v>0.9247</v>
-      </c>
+      <c r="S40" s="5" t="inlineStr"/>
       <c r="T40" s="5" t="n">
         <v>-0.0043</v>
       </c>
       <c r="U40" s="6" t="n">
         <v>-0.46</v>
       </c>
-      <c r="V40" s="5" t="n">
-        <v>-0.0043</v>
-      </c>
-      <c r="W40" s="6" t="n">
-        <v>-0.46</v>
-      </c>
+      <c r="V40" s="5" t="inlineStr"/>
+      <c r="W40" s="6" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>BRDDSF01</t>
+          <t>BRDDBES1</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -3032,11 +3024,11 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D41" s="4" t="n">
-        <v>368</v>
+        <v>240</v>
       </c>
       <c r="E41" s="5" t="inlineStr"/>
       <c r="F41" s="5" t="inlineStr"/>
@@ -3052,19 +3044,27 @@
       <c r="P41" s="5" t="n">
         <v>0.929</v>
       </c>
-      <c r="Q41" s="5" t="inlineStr"/>
+      <c r="Q41" s="5" t="n">
+        <v>0.929</v>
+      </c>
       <c r="R41" s="5" t="n">
         <v>0.9247</v>
       </c>
-      <c r="S41" s="5" t="inlineStr"/>
+      <c r="S41" s="5" t="n">
+        <v>0.9247</v>
+      </c>
       <c r="T41" s="5" t="n">
         <v>-0.0043</v>
       </c>
       <c r="U41" s="6" t="n">
         <v>-0.46</v>
       </c>
-      <c r="V41" s="5" t="inlineStr"/>
-      <c r="W41" s="6" t="inlineStr"/>
+      <c r="V41" s="5" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="W41" s="6" t="n">
+        <v>-0.46</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -3136,12 +3136,12 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>GLADNL1</t>
+          <t>GSTONE3</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>GLADSTONE POWER STATION</t>
+          <t>Gladstone Power Station</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="D43" s="4" t="n">
-        <v>25</v>
+        <v>280</v>
       </c>
       <c r="E43" s="5" t="n">
         <v>0.9855</v>
@@ -3203,7 +3203,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>GSTONE3</t>
+          <t>GSTONE4</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -3270,12 +3270,12 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>GSTONE4</t>
+          <t>GLADNL1</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Gladstone Power Station</t>
+          <t>GLADSTONE POWER STATION</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -3284,7 +3284,7 @@
         </is>
       </c>
       <c r="D45" s="4" t="n">
-        <v>280</v>
+        <v>25</v>
       </c>
       <c r="E45" s="5" t="n">
         <v>0.9855</v>
@@ -3337,7 +3337,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>GSTONE5</t>
+          <t>GSTONE6</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -3404,7 +3404,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>GSTONE6</t>
+          <t>GSTONE5</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -4173,12 +4173,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>CHILDSF1</t>
+          <t>SRSF1</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Childers Solar Farm</t>
+          <t>Susan River Solar Farm</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -4187,7 +4187,7 @@
         </is>
       </c>
       <c r="D60" s="4" t="n">
-        <v>64.38</v>
+        <v>85.26000000000001</v>
       </c>
       <c r="E60" s="5" t="inlineStr"/>
       <c r="F60" s="5" t="inlineStr"/>
@@ -4234,12 +4234,12 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>SRSF1</t>
+          <t>CHILDSF1</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Susan River Solar Farm</t>
+          <t>Childers Solar Farm</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -4248,7 +4248,7 @@
         </is>
       </c>
       <c r="D61" s="4" t="n">
-        <v>85.26000000000001</v>
+        <v>64.38</v>
       </c>
       <c r="E61" s="5" t="inlineStr"/>
       <c r="F61" s="5" t="inlineStr"/>
@@ -4295,7 +4295,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>MSTUART1</t>
+          <t>MSTUART3</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -4309,7 +4309,7 @@
         </is>
       </c>
       <c r="D62" s="4" t="n">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="E62" s="5" t="n">
         <v>1.0156</v>
@@ -4429,7 +4429,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>MSTUART3</t>
+          <t>MSTUART1</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="D64" s="4" t="n">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="E64" s="5" t="n">
         <v>1.0156</v>
@@ -4551,7 +4551,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>KEPBL1</t>
+          <t>KEPBG1</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -4572,27 +4572,43 @@
       <c r="G66" s="5" t="inlineStr"/>
       <c r="H66" s="5" t="inlineStr"/>
       <c r="I66" s="5" t="inlineStr"/>
-      <c r="J66" s="5" t="inlineStr"/>
-      <c r="K66" s="5" t="inlineStr"/>
-      <c r="L66" s="5" t="inlineStr"/>
-      <c r="M66" s="5" t="inlineStr"/>
-      <c r="N66" s="5" t="inlineStr"/>
+      <c r="J66" s="5" t="n">
+        <v>0.9581</v>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>0.9912</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>0.9808</v>
+      </c>
+      <c r="M66" s="5" t="n">
+        <v>0.9667</v>
+      </c>
+      <c r="N66" s="5" t="n">
+        <v>0.9703000000000001</v>
+      </c>
       <c r="O66" s="5" t="inlineStr"/>
-      <c r="P66" s="5" t="inlineStr"/>
+      <c r="P66" s="5" t="n">
+        <v>0.9813</v>
+      </c>
       <c r="Q66" s="5" t="inlineStr"/>
       <c r="R66" s="5" t="n">
         <v>0.9574</v>
       </c>
       <c r="S66" s="5" t="inlineStr"/>
-      <c r="T66" s="5" t="inlineStr"/>
-      <c r="U66" s="6" t="inlineStr"/>
+      <c r="T66" s="5" t="n">
+        <v>-0.0239</v>
+      </c>
+      <c r="U66" s="6" t="n">
+        <v>-2.44</v>
+      </c>
       <c r="V66" s="5" t="inlineStr"/>
       <c r="W66" s="6" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>KEPWF1</t>
+          <t>KEPSF1</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -4602,11 +4618,11 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D67" s="4" t="n">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="E67" s="5" t="inlineStr"/>
       <c r="F67" s="5" t="inlineStr"/>
@@ -4649,21 +4665,21 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>KEPBG1</t>
+          <t>KEPWF1</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Kennedy Energy Park Battery</t>
+          <t>Kennedy Energy Park</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D68" s="4" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="E68" s="5" t="inlineStr"/>
       <c r="F68" s="5" t="inlineStr"/>
@@ -4706,57 +4722,41 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>KEPSF1</t>
+          <t>KEPBL1</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Kennedy Energy Park</t>
+          <t>Kennedy Energy Park Battery</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D69" s="4" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E69" s="5" t="inlineStr"/>
       <c r="F69" s="5" t="inlineStr"/>
       <c r="G69" s="5" t="inlineStr"/>
       <c r="H69" s="5" t="inlineStr"/>
       <c r="I69" s="5" t="inlineStr"/>
-      <c r="J69" s="5" t="n">
-        <v>0.9581</v>
-      </c>
-      <c r="K69" s="5" t="n">
-        <v>0.9912</v>
-      </c>
-      <c r="L69" s="5" t="n">
-        <v>0.9808</v>
-      </c>
-      <c r="M69" s="5" t="n">
-        <v>0.9667</v>
-      </c>
-      <c r="N69" s="5" t="n">
-        <v>0.9703000000000001</v>
-      </c>
+      <c r="J69" s="5" t="inlineStr"/>
+      <c r="K69" s="5" t="inlineStr"/>
+      <c r="L69" s="5" t="inlineStr"/>
+      <c r="M69" s="5" t="inlineStr"/>
+      <c r="N69" s="5" t="inlineStr"/>
       <c r="O69" s="5" t="inlineStr"/>
-      <c r="P69" s="5" t="n">
-        <v>0.9813</v>
-      </c>
+      <c r="P69" s="5" t="inlineStr"/>
       <c r="Q69" s="5" t="inlineStr"/>
       <c r="R69" s="5" t="n">
         <v>0.9574</v>
       </c>
       <c r="S69" s="5" t="inlineStr"/>
-      <c r="T69" s="5" t="n">
-        <v>-0.0239</v>
-      </c>
-      <c r="U69" s="6" t="n">
-        <v>-2.44</v>
-      </c>
+      <c r="T69" s="5" t="inlineStr"/>
+      <c r="U69" s="6" t="inlineStr"/>
       <c r="V69" s="5" t="inlineStr"/>
       <c r="W69" s="6" t="inlineStr"/>
     </row>
@@ -4810,7 +4810,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>KAREEYA2</t>
+          <t>KAREEYA1</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -4877,7 +4877,7 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>KAREEYA5</t>
+          <t>KAREEYA2</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -4891,7 +4891,7 @@
         </is>
       </c>
       <c r="D72" s="4" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E72" s="5" t="n">
         <v>1.069</v>
@@ -4944,7 +4944,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>KAREEYA4</t>
+          <t>KAREEYA3</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -5011,7 +5011,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>KAREEYA3</t>
+          <t>KAREEYA5</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="D74" s="4" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E74" s="5" t="n">
         <v>1.069</v>
@@ -5078,7 +5078,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>KAREEYA1</t>
+          <t>KAREEYA4</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -5554,12 +5554,12 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>DDPS1</t>
+          <t>BRAEMAR1</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Darling Downs Power Station</t>
+          <t>Braemar Power Station</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -5568,7 +5568,7 @@
         </is>
       </c>
       <c r="D83" s="4" t="n">
-        <v>644</v>
+        <v>168</v>
       </c>
       <c r="E83" s="5" t="n">
         <v>0.9567</v>
@@ -5621,12 +5621,12 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>BRAEMAR5</t>
+          <t>BRAEMAR2</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Braemar 2 Power Station</t>
+          <t>Braemar Power Station</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="D84" s="4" t="n">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E84" s="5" t="n">
         <v>0.9567</v>
@@ -5755,12 +5755,12 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>BRAEMAR2</t>
+          <t>BRAEMAR5</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Braemar Power Station</t>
+          <t>Braemar 2 Power Station</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -5769,7 +5769,7 @@
         </is>
       </c>
       <c r="D86" s="4" t="n">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="E86" s="5" t="n">
         <v>0.9567</v>
@@ -5822,12 +5822,12 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>BRAEMAR1</t>
+          <t>BRAEMAR6</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Braemar Power Station</t>
+          <t>Braemar 2 Power Station</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -5836,7 +5836,7 @@
         </is>
       </c>
       <c r="D87" s="4" t="n">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="E87" s="5" t="n">
         <v>0.9567</v>
@@ -5956,12 +5956,12 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>BRAEMAR6</t>
+          <t>DDPS1</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Braemar 2 Power Station</t>
+          <t>Darling Downs Power Station</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -5970,7 +5970,7 @@
         </is>
       </c>
       <c r="D89" s="4" t="n">
-        <v>173</v>
+        <v>644</v>
       </c>
       <c r="E89" s="5" t="n">
         <v>0.9567</v>
@@ -6332,7 +6332,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>TARONG#2</t>
+          <t>TARONG#3</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -6399,7 +6399,7 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>TARONG#3</t>
+          <t>TARONG#2</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -7720,12 +7720,12 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>OAKEY1SF</t>
+          <t>OAKEY2SF</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>Oakey 1 Solar Farm</t>
+          <t>Oakey 2 Solar Farm</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
@@ -7734,14 +7734,12 @@
         </is>
       </c>
       <c r="D117" s="4" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="E117" s="5" t="inlineStr"/>
       <c r="F117" s="5" t="inlineStr"/>
       <c r="G117" s="5" t="inlineStr"/>
-      <c r="H117" s="5" t="n">
-        <v>0.9826</v>
-      </c>
+      <c r="H117" s="5" t="inlineStr"/>
       <c r="I117" s="5" t="n">
         <v>0.9824000000000001</v>
       </c>
@@ -7781,12 +7779,12 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>OAKEY2SF</t>
+          <t>OAKEY1SF</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>Oakey 2 Solar Farm</t>
+          <t>Oakey 1 Solar Farm</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
@@ -7795,12 +7793,14 @@
         </is>
       </c>
       <c r="D118" s="4" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="E118" s="5" t="inlineStr"/>
       <c r="F118" s="5" t="inlineStr"/>
       <c r="G118" s="5" t="inlineStr"/>
-      <c r="H118" s="5" t="inlineStr"/>
+      <c r="H118" s="5" t="n">
+        <v>0.9826</v>
+      </c>
       <c r="I118" s="5" t="n">
         <v>0.9824000000000001</v>
       </c>
@@ -7840,12 +7840,12 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>WARWSF2</t>
+          <t>YARANSF1</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>Warwick Solar Farm 2</t>
+          <t>Yarranlea Solar Farm</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
@@ -7854,13 +7854,15 @@
         </is>
       </c>
       <c r="D119" s="4" t="n">
-        <v>39</v>
+        <v>121</v>
       </c>
       <c r="E119" s="5" t="inlineStr"/>
       <c r="F119" s="5" t="inlineStr"/>
       <c r="G119" s="5" t="inlineStr"/>
       <c r="H119" s="5" t="inlineStr"/>
-      <c r="I119" s="5" t="inlineStr"/>
+      <c r="I119" s="5" t="n">
+        <v>0.9877</v>
+      </c>
       <c r="J119" s="5" t="n">
         <v>0.9851</v>
       </c>
@@ -7897,45 +7899,41 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>WARWSF1</t>
+          <t>DULAWF1</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warwick Solar Farm 1 </t>
+          <t>Dulacca Wind Farm</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D120" s="4" t="n">
-        <v>39</v>
+        <v>180</v>
       </c>
       <c r="E120" s="5" t="inlineStr"/>
       <c r="F120" s="5" t="inlineStr"/>
       <c r="G120" s="5" t="inlineStr"/>
       <c r="H120" s="5" t="inlineStr"/>
       <c r="I120" s="5" t="inlineStr"/>
-      <c r="J120" s="5" t="n">
-        <v>0.9851</v>
-      </c>
-      <c r="K120" s="5" t="n">
-        <v>0.9789</v>
-      </c>
+      <c r="J120" s="5" t="inlineStr"/>
+      <c r="K120" s="5" t="inlineStr"/>
       <c r="L120" s="5" t="n">
-        <v>0.9861</v>
+        <v>0.9540999999999999</v>
       </c>
       <c r="M120" s="5" t="n">
-        <v>0.9913999999999999</v>
+        <v>0.9776</v>
       </c>
       <c r="N120" s="5" t="n">
-        <v>0.9847</v>
+        <v>0.977</v>
       </c>
       <c r="O120" s="5" t="inlineStr"/>
       <c r="P120" s="5" t="n">
-        <v>0.9888</v>
+        <v>0.9853</v>
       </c>
       <c r="Q120" s="5" t="inlineStr"/>
       <c r="R120" s="5" t="n">
@@ -7943,10 +7941,10 @@
       </c>
       <c r="S120" s="5" t="inlineStr"/>
       <c r="T120" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0017</v>
       </c>
       <c r="U120" s="6" t="n">
-        <v>-0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V120" s="5" t="inlineStr"/>
       <c r="W120" s="6" t="inlineStr"/>
@@ -7954,41 +7952,45 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>DULAWF1</t>
+          <t>WARWSF1</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>Dulacca Wind Farm</t>
+          <t xml:space="preserve">Warwick Solar Farm 1 </t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D121" s="4" t="n">
-        <v>180</v>
+        <v>39</v>
       </c>
       <c r="E121" s="5" t="inlineStr"/>
       <c r="F121" s="5" t="inlineStr"/>
       <c r="G121" s="5" t="inlineStr"/>
       <c r="H121" s="5" t="inlineStr"/>
       <c r="I121" s="5" t="inlineStr"/>
-      <c r="J121" s="5" t="inlineStr"/>
-      <c r="K121" s="5" t="inlineStr"/>
+      <c r="J121" s="5" t="n">
+        <v>0.9851</v>
+      </c>
+      <c r="K121" s="5" t="n">
+        <v>0.9789</v>
+      </c>
       <c r="L121" s="5" t="n">
-        <v>0.9540999999999999</v>
+        <v>0.9861</v>
       </c>
       <c r="M121" s="5" t="n">
-        <v>0.9776</v>
+        <v>0.9913999999999999</v>
       </c>
       <c r="N121" s="5" t="n">
-        <v>0.977</v>
+        <v>0.9847</v>
       </c>
       <c r="O121" s="5" t="inlineStr"/>
       <c r="P121" s="5" t="n">
-        <v>0.9853</v>
+        <v>0.9888</v>
       </c>
       <c r="Q121" s="5" t="inlineStr"/>
       <c r="R121" s="5" t="n">
@@ -7996,10 +7998,10 @@
       </c>
       <c r="S121" s="5" t="inlineStr"/>
       <c r="T121" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.0018</v>
       </c>
       <c r="U121" s="6" t="n">
-        <v>0.17</v>
+        <v>-0.18</v>
       </c>
       <c r="V121" s="5" t="inlineStr"/>
       <c r="W121" s="6" t="inlineStr"/>
@@ -8007,12 +8009,12 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>YARANSF1</t>
+          <t>WARWSF2</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>Yarranlea Solar Farm</t>
+          <t>Warwick Solar Farm 2</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
@@ -8021,15 +8023,13 @@
         </is>
       </c>
       <c r="D122" s="4" t="n">
-        <v>121</v>
+        <v>39</v>
       </c>
       <c r="E122" s="5" t="inlineStr"/>
       <c r="F122" s="5" t="inlineStr"/>
       <c r="G122" s="5" t="inlineStr"/>
       <c r="H122" s="5" t="inlineStr"/>
-      <c r="I122" s="5" t="n">
-        <v>0.9877</v>
-      </c>
+      <c r="I122" s="5" t="inlineStr"/>
       <c r="J122" s="5" t="n">
         <v>0.9851</v>
       </c>
@@ -8550,70 +8550,62 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>DG_QLD1</t>
+          <t>SNB01</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>QLD1 Dummy Generator</t>
-        </is>
-      </c>
-      <c r="C131" s="3" t="inlineStr"/>
+          <t>Supernode BESS</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
       <c r="D131" s="4" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E131" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F131" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G131" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H131" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I131" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J131" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K131" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L131" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M131" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N131" s="5" t="n">
-        <v>1</v>
-      </c>
+        <v>337.4</v>
+      </c>
+      <c r="E131" s="5" t="inlineStr"/>
+      <c r="F131" s="5" t="inlineStr"/>
+      <c r="G131" s="5" t="inlineStr"/>
+      <c r="H131" s="5" t="inlineStr"/>
+      <c r="I131" s="5" t="inlineStr"/>
+      <c r="J131" s="5" t="inlineStr"/>
+      <c r="K131" s="5" t="inlineStr"/>
+      <c r="L131" s="5" t="inlineStr"/>
+      <c r="M131" s="5" t="inlineStr"/>
+      <c r="N131" s="5" t="inlineStr"/>
       <c r="O131" s="5" t="inlineStr"/>
       <c r="P131" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="Q131" s="5" t="inlineStr"/>
+      <c r="Q131" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="R131" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="S131" s="5" t="inlineStr"/>
+      <c r="S131" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="T131" s="5" t="n">
         <v>0</v>
       </c>
       <c r="U131" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="V131" s="5" t="inlineStr"/>
-      <c r="W131" s="6" t="inlineStr"/>
+      <c r="V131" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W131" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>SNB01</t>
+          <t>SNB02</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -8668,57 +8660,65 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>SNB02</t>
+          <t>DG_QLD1</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>Supernode BESS</t>
-        </is>
-      </c>
-      <c r="C133" s="3" t="inlineStr">
-        <is>
-          <t>Battery</t>
-        </is>
-      </c>
+          <t>QLD1 Dummy Generator</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr"/>
       <c r="D133" s="4" t="n">
-        <v>337.4</v>
-      </c>
-      <c r="E133" s="5" t="inlineStr"/>
-      <c r="F133" s="5" t="inlineStr"/>
-      <c r="G133" s="5" t="inlineStr"/>
-      <c r="H133" s="5" t="inlineStr"/>
-      <c r="I133" s="5" t="inlineStr"/>
-      <c r="J133" s="5" t="inlineStr"/>
-      <c r="K133" s="5" t="inlineStr"/>
-      <c r="L133" s="5" t="inlineStr"/>
-      <c r="M133" s="5" t="inlineStr"/>
-      <c r="N133" s="5" t="inlineStr"/>
+        <v>3000</v>
+      </c>
+      <c r="E133" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F133" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G133" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H133" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I133" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J133" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K133" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L133" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M133" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N133" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O133" s="5" t="inlineStr"/>
       <c r="P133" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="Q133" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q133" s="5" t="inlineStr"/>
       <c r="R133" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="S133" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="S133" s="5" t="inlineStr"/>
       <c r="T133" s="5" t="n">
         <v>0</v>
       </c>
       <c r="U133" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="V133" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W133" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="V133" s="5" t="inlineStr"/>
+      <c r="W133" s="6" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
@@ -9250,12 +9250,12 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>STAPYLTON1</t>
+          <t>RPCG</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>Stapylton Renewable Energy Facility</t>
+          <t>Rocky Point Cogeneration Plant</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
@@ -9264,10 +9264,14 @@
         </is>
       </c>
       <c r="D143" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E143" s="5" t="inlineStr"/>
-      <c r="F143" s="5" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="E143" s="5" t="n">
+        <v>1.0078</v>
+      </c>
+      <c r="F143" s="5" t="n">
+        <v>1.008</v>
+      </c>
       <c r="G143" s="5" t="n">
         <v>1.0112</v>
       </c>
@@ -9313,12 +9317,12 @@
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>RPCG</t>
+          <t>STAPYLTON1</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>Rocky Point Cogeneration Plant</t>
+          <t>Stapylton Renewable Energy Facility</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
@@ -9327,14 +9331,10 @@
         </is>
       </c>
       <c r="D144" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="E144" s="5" t="n">
-        <v>1.0078</v>
-      </c>
-      <c r="F144" s="5" t="n">
-        <v>1.008</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E144" s="5" t="inlineStr"/>
+      <c r="F144" s="5" t="inlineStr"/>
       <c r="G144" s="5" t="n">
         <v>1.0112</v>
       </c>
@@ -9834,12 +9834,12 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>ROCHEDAL</t>
+          <t>EDLRGNRD</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>Rochedale Renewable Energy Facility</t>
+          <t>Roghan Road LFG Power Plant</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
@@ -9848,22 +9848,22 @@
         </is>
       </c>
       <c r="D153" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>1.0067</v>
+        <v>1.0057</v>
       </c>
       <c r="F153" s="5" t="n">
-        <v>1.0091</v>
+        <v>1.0049</v>
       </c>
       <c r="G153" s="5" t="n">
-        <v>1.0114</v>
+        <v>1.0044</v>
       </c>
       <c r="H153" s="5" t="n">
-        <v>1.0123</v>
+        <v>1.0042</v>
       </c>
       <c r="I153" s="5" t="n">
-        <v>1.0121</v>
+        <v>1.0042</v>
       </c>
       <c r="J153" s="5" t="inlineStr"/>
       <c r="K153" s="5" t="inlineStr"/>
@@ -9883,12 +9883,12 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>WHIT1</t>
+          <t>ROCHEDAL</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>Whitwood Road Renewable Energy Facility</t>
+          <t>Rochedale Renewable Energy Facility</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
@@ -9897,22 +9897,22 @@
         </is>
       </c>
       <c r="D154" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>0.9953</v>
+        <v>1.0067</v>
       </c>
       <c r="F154" s="5" t="n">
-        <v>0.9968</v>
+        <v>1.0091</v>
       </c>
       <c r="G154" s="5" t="n">
-        <v>0.9999</v>
+        <v>1.0114</v>
       </c>
       <c r="H154" s="5" t="n">
-        <v>1.0001</v>
+        <v>1.0123</v>
       </c>
       <c r="I154" s="5" t="n">
-        <v>1.0006</v>
+        <v>1.0121</v>
       </c>
       <c r="J154" s="5" t="inlineStr"/>
       <c r="K154" s="5" t="inlineStr"/>
@@ -9932,12 +9932,12 @@
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>EDLRGNRD</t>
+          <t>WHIT1</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>Roghan Road LFG Power Plant</t>
+          <t>Whitwood Road Renewable Energy Facility</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
@@ -9946,22 +9946,22 @@
         </is>
       </c>
       <c r="D155" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>1.0057</v>
+        <v>0.9953</v>
       </c>
       <c r="F155" s="5" t="n">
-        <v>1.0049</v>
+        <v>0.9968</v>
       </c>
       <c r="G155" s="5" t="n">
-        <v>1.0044</v>
+        <v>0.9999</v>
       </c>
       <c r="H155" s="5" t="n">
-        <v>1.0042</v>
+        <v>1.0001</v>
       </c>
       <c r="I155" s="5" t="n">
-        <v>1.0042</v>
+        <v>1.0006</v>
       </c>
       <c r="J155" s="5" t="inlineStr"/>
       <c r="K155" s="5" t="inlineStr"/>
@@ -9986,11 +9986,17 @@
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>Mackay Gas Turbine</t>
-        </is>
-      </c>
-      <c r="C156" s="3" t="n"/>
-      <c r="D156" s="3" t="inlineStr"/>
+          <t>MACKAY GAS TURBINE</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D156" s="4" t="n">
+        <v>30</v>
+      </c>
       <c r="E156" s="5" t="n">
         <v>1.055</v>
       </c>
@@ -10226,22 +10232,18 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>CHBESSG1</t>
+          <t>BBATTERY</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>Chinchilla BESS</t>
-        </is>
-      </c>
-      <c r="C161" s="3" t="inlineStr">
-        <is>
-          <t>Battery</t>
-        </is>
-      </c>
-      <c r="D161" s="4" t="n">
-        <v>134</v>
-      </c>
+          <t>Bouldercombe Battery Project</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D161" s="3" t="inlineStr"/>
       <c r="E161" s="5" t="inlineStr"/>
       <c r="F161" s="5" t="inlineStr"/>
       <c r="G161" s="5" t="inlineStr"/>
@@ -10251,10 +10253,10 @@
       <c r="K161" s="5" t="inlineStr"/>
       <c r="L161" s="5" t="inlineStr"/>
       <c r="M161" s="5" t="n">
-        <v>0.9588</v>
+        <v>0.9198</v>
       </c>
       <c r="N161" s="5" t="n">
-        <v>0.9611</v>
+        <v>0.9166</v>
       </c>
       <c r="O161" s="5" t="inlineStr"/>
       <c r="P161" s="5" t="inlineStr"/>
@@ -10269,18 +10271,22 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>BBATTERY</t>
+          <t>CHBESSG1</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>Bouldercombe Battery Project</t>
-        </is>
-      </c>
-      <c r="C162" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D162" s="3" t="inlineStr"/>
+          <t>Chinchilla BESS</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="D162" s="4" t="n">
+        <v>134</v>
+      </c>
       <c r="E162" s="5" t="inlineStr"/>
       <c r="F162" s="5" t="inlineStr"/>
       <c r="G162" s="5" t="inlineStr"/>
@@ -10290,10 +10296,10 @@
       <c r="K162" s="5" t="inlineStr"/>
       <c r="L162" s="5" t="inlineStr"/>
       <c r="M162" s="5" t="n">
-        <v>0.9198</v>
+        <v>0.9588</v>
       </c>
       <c r="N162" s="5" t="n">
-        <v>0.9166</v>
+        <v>0.9611</v>
       </c>
       <c r="O162" s="5" t="inlineStr"/>
       <c r="P162" s="5" t="inlineStr"/>
@@ -10588,7 +10594,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>DAYDSF1</t>
+          <t>HAYMSF1</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
@@ -10628,7 +10634,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>HAYMSF1</t>
+          <t>DAYDSF1</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr"/>
@@ -10748,13 +10754,13 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>HUGSF1</t>
+          <t>KSP1</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="5" t="inlineStr"/>
       <c r="D10" s="5" t="n">
-        <v>1.0115</v>
+        <v>1.0149</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>0.8842</v>
@@ -10832,13 +10838,13 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>KSP1</t>
+          <t>HUGSF1</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="5" t="inlineStr"/>
       <c r="D12" s="5" t="n">
-        <v>1.0149</v>
+        <v>1.0115</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>0.8842</v>
@@ -10906,16 +10912,20 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>MIDDLSF1</t>
+          <t>EMERASF1</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr"/>
       <c r="C14" s="5" t="inlineStr"/>
       <c r="D14" s="5" t="inlineStr"/>
-      <c r="E14" s="5" t="inlineStr"/>
-      <c r="F14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="n">
+        <v>0.8778</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>0.8712</v>
+      </c>
       <c r="G14" s="5" t="n">
-        <v>0.882</v>
+        <v>0.8864</v>
       </c>
       <c r="H14" s="5" t="n">
         <v>0.9237</v>
@@ -10942,20 +10952,16 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>EMERASF1</t>
+          <t>MIDDLSF1</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr"/>
       <c r="C15" s="5" t="inlineStr"/>
       <c r="D15" s="5" t="inlineStr"/>
-      <c r="E15" s="5" t="n">
-        <v>0.8778</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>0.8712</v>
-      </c>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr"/>
       <c r="G15" s="5" t="n">
-        <v>0.8864</v>
+        <v>0.882</v>
       </c>
       <c r="H15" s="5" t="n">
         <v>0.9237</v>
@@ -11022,15 +11028,13 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>BARCSF1</t>
+          <t>LRSF1</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr"/>
-      <c r="C17" s="5" t="n">
-        <v>0.9385</v>
-      </c>
+      <c r="C17" s="5" t="inlineStr"/>
       <c r="D17" s="5" t="n">
-        <v>0.9715</v>
+        <v>0.9689</v>
       </c>
       <c r="E17" s="5" t="n">
         <v>0.8934</v>
@@ -11066,13 +11070,15 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>LRSF1</t>
+          <t>BARCSF1</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr"/>
-      <c r="C18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>0.9385</v>
+      </c>
       <c r="D18" s="5" t="n">
-        <v>0.9689</v>
+        <v>0.9715</v>
       </c>
       <c r="E18" s="5" t="n">
         <v>0.8934</v>
@@ -11148,7 +11154,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>KIDSPHG2</t>
+          <t>KIDSPHG1</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr"/>
@@ -11174,7 +11180,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>KIDSPHG1</t>
+          <t>KIDSPHG2</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr"/>
@@ -11228,7 +11234,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>CALL_B_2</t>
+          <t>CALL_B_1</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
@@ -11274,7 +11280,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>CALL_B_1</t>
+          <t>CALL_B_2</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
@@ -11458,7 +11464,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>OAKY2</t>
+          <t>OAKYCREK</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
@@ -11504,7 +11510,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>OAKYCREK</t>
+          <t>OAKY2</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
@@ -11550,7 +11556,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>CALLNL4</t>
+          <t>CALL_A_4</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
@@ -11588,7 +11594,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>CALL_A_4</t>
+          <t>CALLNL4</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
@@ -11672,7 +11678,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>STAN-3</t>
+          <t>STAN-1</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
@@ -11718,7 +11724,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>STAN-4</t>
+          <t>STAN-3</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
@@ -11764,7 +11770,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>STAN-1</t>
+          <t>STAN-4</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
@@ -11994,7 +12000,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>BRDDBES1</t>
+          <t>BRDDSF01</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr"/>
@@ -12011,20 +12017,16 @@
       <c r="M40" s="5" t="n">
         <v>0.929</v>
       </c>
-      <c r="N40" s="5" t="n">
-        <v>0.929</v>
-      </c>
+      <c r="N40" s="5" t="inlineStr"/>
       <c r="O40" s="5" t="n">
         <v>0.9247</v>
       </c>
-      <c r="P40" s="5" t="n">
-        <v>0.9247</v>
-      </c>
+      <c r="P40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>BRDDSF01</t>
+          <t>BRDDBES1</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr"/>
@@ -12041,11 +12043,15 @@
       <c r="M41" s="5" t="n">
         <v>0.929</v>
       </c>
-      <c r="N41" s="5" t="inlineStr"/>
+      <c r="N41" s="5" t="n">
+        <v>0.929</v>
+      </c>
       <c r="O41" s="5" t="n">
         <v>0.9247</v>
       </c>
-      <c r="P41" s="5" t="inlineStr"/>
+      <c r="P41" s="5" t="n">
+        <v>0.9247</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -12096,7 +12102,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>GLADNL1</t>
+          <t>GSTONE3</t>
         </is>
       </c>
       <c r="B43" s="5" t="n">
@@ -12142,7 +12148,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>GSTONE3</t>
+          <t>GSTONE4</t>
         </is>
       </c>
       <c r="B44" s="5" t="n">
@@ -12188,7 +12194,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>GSTONE4</t>
+          <t>GLADNL1</t>
         </is>
       </c>
       <c r="B45" s="5" t="n">
@@ -12234,7 +12240,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>GSTONE5</t>
+          <t>GSTONE6</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
@@ -12280,7 +12286,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>GSTONE6</t>
+          <t>GSTONE5</t>
         </is>
       </c>
       <c r="B47" s="5" t="n">
@@ -12772,7 +12778,7 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>CHILDSF1</t>
+          <t>SRSF1</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr"/>
@@ -12812,7 +12818,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>SRSF1</t>
+          <t>CHILDSF1</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr"/>
@@ -12852,7 +12858,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>MSTUART1</t>
+          <t>MSTUART3</t>
         </is>
       </c>
       <c r="B62" s="5" t="n">
@@ -12944,7 +12950,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>MSTUART3</t>
+          <t>MSTUART1</t>
         </is>
       </c>
       <c r="B64" s="5" t="n">
@@ -13024,7 +13030,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>KEPBL1</t>
+          <t>KEPBG1</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr"/>
@@ -13032,13 +13038,25 @@
       <c r="D66" s="5" t="inlineStr"/>
       <c r="E66" s="5" t="inlineStr"/>
       <c r="F66" s="5" t="inlineStr"/>
-      <c r="G66" s="5" t="inlineStr"/>
-      <c r="H66" s="5" t="inlineStr"/>
-      <c r="I66" s="5" t="inlineStr"/>
-      <c r="J66" s="5" t="inlineStr"/>
-      <c r="K66" s="5" t="inlineStr"/>
+      <c r="G66" s="5" t="n">
+        <v>0.9581</v>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>0.9912</v>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>0.9808</v>
+      </c>
+      <c r="J66" s="5" t="n">
+        <v>0.9667</v>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>0.9703000000000001</v>
+      </c>
       <c r="L66" s="5" t="inlineStr"/>
-      <c r="M66" s="5" t="inlineStr"/>
+      <c r="M66" s="5" t="n">
+        <v>0.9813</v>
+      </c>
       <c r="N66" s="5" t="inlineStr"/>
       <c r="O66" s="5" t="n">
         <v>0.9574</v>
@@ -13048,7 +13066,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>KEPWF1</t>
+          <t>KEPSF1</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr"/>
@@ -13084,7 +13102,7 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>KEPBG1</t>
+          <t>KEPWF1</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr"/>
@@ -13120,7 +13138,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>KEPSF1</t>
+          <t>KEPBL1</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr"/>
@@ -13128,25 +13146,13 @@
       <c r="D69" s="5" t="inlineStr"/>
       <c r="E69" s="5" t="inlineStr"/>
       <c r="F69" s="5" t="inlineStr"/>
-      <c r="G69" s="5" t="n">
-        <v>0.9581</v>
-      </c>
-      <c r="H69" s="5" t="n">
-        <v>0.9912</v>
-      </c>
-      <c r="I69" s="5" t="n">
-        <v>0.9808</v>
-      </c>
-      <c r="J69" s="5" t="n">
-        <v>0.9667</v>
-      </c>
-      <c r="K69" s="5" t="n">
-        <v>0.9703000000000001</v>
-      </c>
+      <c r="G69" s="5" t="inlineStr"/>
+      <c r="H69" s="5" t="inlineStr"/>
+      <c r="I69" s="5" t="inlineStr"/>
+      <c r="J69" s="5" t="inlineStr"/>
+      <c r="K69" s="5" t="inlineStr"/>
       <c r="L69" s="5" t="inlineStr"/>
-      <c r="M69" s="5" t="n">
-        <v>0.9813</v>
-      </c>
+      <c r="M69" s="5" t="inlineStr"/>
       <c r="N69" s="5" t="inlineStr"/>
       <c r="O69" s="5" t="n">
         <v>0.9574</v>
@@ -13182,7 +13188,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>KAREEYA2</t>
+          <t>KAREEYA1</t>
         </is>
       </c>
       <c r="B71" s="5" t="n">
@@ -13228,7 +13234,7 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>KAREEYA5</t>
+          <t>KAREEYA2</t>
         </is>
       </c>
       <c r="B72" s="5" t="n">
@@ -13274,7 +13280,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>KAREEYA4</t>
+          <t>KAREEYA3</t>
         </is>
       </c>
       <c r="B73" s="5" t="n">
@@ -13320,7 +13326,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>KAREEYA3</t>
+          <t>KAREEYA5</t>
         </is>
       </c>
       <c r="B74" s="5" t="n">
@@ -13366,7 +13372,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>KAREEYA1</t>
+          <t>KAREEYA4</t>
         </is>
       </c>
       <c r="B75" s="5" t="n">
@@ -13658,7 +13664,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>DDPS1</t>
+          <t>BRAEMAR1</t>
         </is>
       </c>
       <c r="B83" s="5" t="n">
@@ -13704,7 +13710,7 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>BRAEMAR5</t>
+          <t>BRAEMAR2</t>
         </is>
       </c>
       <c r="B84" s="5" t="n">
@@ -13796,7 +13802,7 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>BRAEMAR2</t>
+          <t>BRAEMAR5</t>
         </is>
       </c>
       <c r="B86" s="5" t="n">
@@ -13842,7 +13848,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>BRAEMAR1</t>
+          <t>BRAEMAR6</t>
         </is>
       </c>
       <c r="B87" s="5" t="n">
@@ -13934,7 +13940,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>BRAEMAR6</t>
+          <t>DDPS1</t>
         </is>
       </c>
       <c r="B89" s="5" t="n">
@@ -14180,7 +14186,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>TARONG#2</t>
+          <t>TARONG#3</t>
         </is>
       </c>
       <c r="B95" s="5" t="n">
@@ -14226,7 +14232,7 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>TARONG#3</t>
+          <t>TARONG#2</t>
         </is>
       </c>
       <c r="B96" s="5" t="n">
@@ -15106,15 +15112,13 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>OAKEY1SF</t>
+          <t>OAKEY2SF</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr"/>
       <c r="C117" s="5" t="inlineStr"/>
       <c r="D117" s="5" t="inlineStr"/>
-      <c r="E117" s="5" t="n">
-        <v>0.9826</v>
-      </c>
+      <c r="E117" s="5" t="inlineStr"/>
       <c r="F117" s="5" t="n">
         <v>0.9824000000000001</v>
       </c>
@@ -15146,13 +15150,15 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>OAKEY2SF</t>
+          <t>OAKEY1SF</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr"/>
       <c r="C118" s="5" t="inlineStr"/>
       <c r="D118" s="5" t="inlineStr"/>
-      <c r="E118" s="5" t="inlineStr"/>
+      <c r="E118" s="5" t="n">
+        <v>0.9826</v>
+      </c>
       <c r="F118" s="5" t="n">
         <v>0.9824000000000001</v>
       </c>
@@ -15184,14 +15190,16 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>WARWSF2</t>
+          <t>YARANSF1</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr"/>
       <c r="C119" s="5" t="inlineStr"/>
       <c r="D119" s="5" t="inlineStr"/>
       <c r="E119" s="5" t="inlineStr"/>
-      <c r="F119" s="5" t="inlineStr"/>
+      <c r="F119" s="5" t="n">
+        <v>0.9877</v>
+      </c>
       <c r="G119" s="5" t="n">
         <v>0.9851</v>
       </c>
@@ -15220,7 +15228,7 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>WARWSF1</t>
+          <t>DULAWF1</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr"/>
@@ -15228,24 +15236,20 @@
       <c r="D120" s="5" t="inlineStr"/>
       <c r="E120" s="5" t="inlineStr"/>
       <c r="F120" s="5" t="inlineStr"/>
-      <c r="G120" s="5" t="n">
-        <v>0.9851</v>
-      </c>
-      <c r="H120" s="5" t="n">
-        <v>0.9789</v>
-      </c>
+      <c r="G120" s="5" t="inlineStr"/>
+      <c r="H120" s="5" t="inlineStr"/>
       <c r="I120" s="5" t="n">
-        <v>0.9861</v>
+        <v>0.9540999999999999</v>
       </c>
       <c r="J120" s="5" t="n">
-        <v>0.9913999999999999</v>
+        <v>0.9776</v>
       </c>
       <c r="K120" s="5" t="n">
-        <v>0.9847</v>
+        <v>0.977</v>
       </c>
       <c r="L120" s="5" t="inlineStr"/>
       <c r="M120" s="5" t="n">
-        <v>0.9888</v>
+        <v>0.9853</v>
       </c>
       <c r="N120" s="5" t="inlineStr"/>
       <c r="O120" s="5" t="n">
@@ -15256,7 +15260,7 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>DULAWF1</t>
+          <t>WARWSF1</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr"/>
@@ -15264,20 +15268,24 @@
       <c r="D121" s="5" t="inlineStr"/>
       <c r="E121" s="5" t="inlineStr"/>
       <c r="F121" s="5" t="inlineStr"/>
-      <c r="G121" s="5" t="inlineStr"/>
-      <c r="H121" s="5" t="inlineStr"/>
+      <c r="G121" s="5" t="n">
+        <v>0.9851</v>
+      </c>
+      <c r="H121" s="5" t="n">
+        <v>0.9789</v>
+      </c>
       <c r="I121" s="5" t="n">
-        <v>0.9540999999999999</v>
+        <v>0.9861</v>
       </c>
       <c r="J121" s="5" t="n">
-        <v>0.9776</v>
+        <v>0.9913999999999999</v>
       </c>
       <c r="K121" s="5" t="n">
-        <v>0.977</v>
+        <v>0.9847</v>
       </c>
       <c r="L121" s="5" t="inlineStr"/>
       <c r="M121" s="5" t="n">
-        <v>0.9853</v>
+        <v>0.9888</v>
       </c>
       <c r="N121" s="5" t="inlineStr"/>
       <c r="O121" s="5" t="n">
@@ -15288,16 +15296,14 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>YARANSF1</t>
+          <t>WARWSF2</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr"/>
       <c r="C122" s="5" t="inlineStr"/>
       <c r="D122" s="5" t="inlineStr"/>
       <c r="E122" s="5" t="inlineStr"/>
-      <c r="F122" s="5" t="n">
-        <v>0.9877</v>
-      </c>
+      <c r="F122" s="5" t="inlineStr"/>
       <c r="G122" s="5" t="n">
         <v>0.9851</v>
       </c>
@@ -15634,53 +15640,37 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>DG_QLD1</t>
-        </is>
-      </c>
-      <c r="B131" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C131" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D131" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E131" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F131" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G131" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H131" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I131" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J131" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K131" s="5" t="n">
-        <v>1</v>
-      </c>
+          <t>SNB01</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="inlineStr"/>
+      <c r="C131" s="5" t="inlineStr"/>
+      <c r="D131" s="5" t="inlineStr"/>
+      <c r="E131" s="5" t="inlineStr"/>
+      <c r="F131" s="5" t="inlineStr"/>
+      <c r="G131" s="5" t="inlineStr"/>
+      <c r="H131" s="5" t="inlineStr"/>
+      <c r="I131" s="5" t="inlineStr"/>
+      <c r="J131" s="5" t="inlineStr"/>
+      <c r="K131" s="5" t="inlineStr"/>
       <c r="L131" s="5" t="inlineStr"/>
       <c r="M131" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="N131" s="5" t="inlineStr"/>
+      <c r="N131" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="O131" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="P131" s="5" t="inlineStr"/>
+      <c r="P131" s="5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>SNB01</t>
+          <t>SNB02</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr"/>
@@ -15710,32 +15700,48 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>SNB02</t>
-        </is>
-      </c>
-      <c r="B133" s="5" t="inlineStr"/>
-      <c r="C133" s="5" t="inlineStr"/>
-      <c r="D133" s="5" t="inlineStr"/>
-      <c r="E133" s="5" t="inlineStr"/>
-      <c r="F133" s="5" t="inlineStr"/>
-      <c r="G133" s="5" t="inlineStr"/>
-      <c r="H133" s="5" t="inlineStr"/>
-      <c r="I133" s="5" t="inlineStr"/>
-      <c r="J133" s="5" t="inlineStr"/>
-      <c r="K133" s="5" t="inlineStr"/>
+          <t>DG_QLD1</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C133" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D133" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F133" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G133" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H133" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I133" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J133" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K133" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="L133" s="5" t="inlineStr"/>
       <c r="M133" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="N133" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="N133" s="5" t="inlineStr"/>
       <c r="O133" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="P133" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="P133" s="5" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
@@ -16082,11 +16088,15 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>STAPYLTON1</t>
-        </is>
-      </c>
-      <c r="B143" s="5" t="inlineStr"/>
-      <c r="C143" s="5" t="inlineStr"/>
+          <t>RPCG</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="n">
+        <v>1.0078</v>
+      </c>
+      <c r="C143" s="5" t="n">
+        <v>1.008</v>
+      </c>
       <c r="D143" s="5" t="n">
         <v>1.0112</v>
       </c>
@@ -16124,15 +16134,11 @@
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>RPCG</t>
-        </is>
-      </c>
-      <c r="B144" s="5" t="n">
-        <v>1.0078</v>
-      </c>
-      <c r="C144" s="5" t="n">
-        <v>1.008</v>
-      </c>
+          <t>STAPYLTON1</t>
+        </is>
+      </c>
+      <c r="B144" s="5" t="inlineStr"/>
+      <c r="C144" s="5" t="inlineStr"/>
       <c r="D144" s="5" t="n">
         <v>1.0112</v>
       </c>
@@ -16468,23 +16474,23 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>ROCHEDAL</t>
+          <t>EDLRGNRD</t>
         </is>
       </c>
       <c r="B153" s="5" t="n">
-        <v>1.0067</v>
+        <v>1.0057</v>
       </c>
       <c r="C153" s="5" t="n">
-        <v>1.0091</v>
+        <v>1.0049</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>1.0114</v>
+        <v>1.0044</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>1.0123</v>
+        <v>1.0042</v>
       </c>
       <c r="F153" s="5" t="n">
-        <v>1.0121</v>
+        <v>1.0042</v>
       </c>
       <c r="G153" s="5" t="inlineStr"/>
       <c r="H153" s="5" t="inlineStr"/>
@@ -16500,23 +16506,23 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>WHIT1</t>
+          <t>ROCHEDAL</t>
         </is>
       </c>
       <c r="B154" s="5" t="n">
-        <v>0.9953</v>
+        <v>1.0067</v>
       </c>
       <c r="C154" s="5" t="n">
-        <v>0.9968</v>
+        <v>1.0091</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>0.9999</v>
+        <v>1.0114</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>1.0001</v>
+        <v>1.0123</v>
       </c>
       <c r="F154" s="5" t="n">
-        <v>1.0006</v>
+        <v>1.0121</v>
       </c>
       <c r="G154" s="5" t="inlineStr"/>
       <c r="H154" s="5" t="inlineStr"/>
@@ -16532,23 +16538,23 @@
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>EDLRGNRD</t>
+          <t>WHIT1</t>
         </is>
       </c>
       <c r="B155" s="5" t="n">
-        <v>1.0057</v>
+        <v>0.9953</v>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1.0049</v>
+        <v>0.9968</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>1.0044</v>
+        <v>0.9999</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>1.0042</v>
+        <v>1.0001</v>
       </c>
       <c r="F155" s="5" t="n">
-        <v>1.0042</v>
+        <v>1.0006</v>
       </c>
       <c r="G155" s="5" t="inlineStr"/>
       <c r="H155" s="5" t="inlineStr"/>
@@ -16730,7 +16736,7 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>CHBESSG1</t>
+          <t>BBATTERY</t>
         </is>
       </c>
       <c r="B161" s="5" t="inlineStr"/>
@@ -16742,10 +16748,10 @@
       <c r="H161" s="5" t="inlineStr"/>
       <c r="I161" s="5" t="inlineStr"/>
       <c r="J161" s="5" t="n">
-        <v>0.9588</v>
+        <v>0.9198</v>
       </c>
       <c r="K161" s="5" t="n">
-        <v>0.9611</v>
+        <v>0.9166</v>
       </c>
       <c r="L161" s="5" t="inlineStr"/>
       <c r="M161" s="5" t="inlineStr"/>
@@ -16756,7 +16762,7 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>BBATTERY</t>
+          <t>CHBESSG1</t>
         </is>
       </c>
       <c r="B162" s="5" t="inlineStr"/>
@@ -16768,10 +16774,10 @@
       <c r="H162" s="5" t="inlineStr"/>
       <c r="I162" s="5" t="inlineStr"/>
       <c r="J162" s="5" t="n">
-        <v>0.9198</v>
+        <v>0.9588</v>
       </c>
       <c r="K162" s="5" t="n">
-        <v>0.9166</v>
+        <v>0.9611</v>
       </c>
       <c r="L162" s="5" t="inlineStr"/>
       <c r="M162" s="5" t="inlineStr"/>
@@ -17029,7 +17035,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>KIDSPHG2</t>
+          <t>KIDSPHG1</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -17058,7 +17064,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>KIDSPHG1</t>
+          <t>KIDSPHG2</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -17145,12 +17151,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>RRSF1</t>
+          <t>KSP1</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Ross River Solar Farm</t>
+          <t>Kidston Solar Project Phase One</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -17174,12 +17180,12 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>KSP1</t>
+          <t>RRSF1</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Kidston Solar Project Phase One</t>
+          <t>Ross River Solar Farm</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -17319,12 +17325,12 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>DAYDSF1</t>
+          <t>HAYMSF1</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Daydream Solar Farm</t>
+          <t>Hayman Solar Farm</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -17348,12 +17354,12 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>HAYMSF1</t>
+          <t>DAYDSF1</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Hayman Solar Farm</t>
+          <t>Daydream Solar Farm</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -17435,12 +17441,12 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>BARCSF1</t>
+          <t>CLERMSF1</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Barcaldine Solar Farm</t>
+          <t>Clermont Solar Farm</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -17464,12 +17470,12 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>CLERMSF1</t>
+          <t>LRSF1</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Clermont Solar Farm</t>
+          <t>Longreach Solar Farm</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -17493,12 +17499,12 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>LRSF1</t>
+          <t>BARCSF1</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Longreach Solar Farm</t>
+          <t>Barcaldine Solar Farm</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -17551,12 +17557,12 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>MIDDLSF1</t>
+          <t>EMERASF1</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Middlemount Solar Farm</t>
+          <t>Emerald Solar Park</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -17580,12 +17586,12 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>EMERASF1</t>
+          <t>MIDDLSF1</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Emerald Solar Park</t>
+          <t>Middlemount Solar Farm</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -17653,7 +17659,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>MSTUART1</t>
+          <t>MSTUART3</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -17711,7 +17717,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>MSTUART3</t>
+          <t>MSTUART1</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -17943,12 +17949,12 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>BRAEMAR6</t>
+          <t>BRAEMAR1</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Braemar 2 Power Station</t>
+          <t>Braemar Power Station</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -17972,12 +17978,12 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>BRAEMAR7</t>
+          <t>BRAEMAR2</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Braemar 2 Power Station</t>
+          <t>Braemar Power Station</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -18001,7 +18007,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>BRAEMAR1</t>
+          <t>BRAEMAR3</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -18030,12 +18036,12 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>BRAEMAR2</t>
+          <t>BRAEMAR5</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Braemar Power Station</t>
+          <t>Braemar 2 Power Station</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -18059,12 +18065,12 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>BRAEMAR3</t>
+          <t>BRAEMAR6</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Braemar Power Station</t>
+          <t>Braemar 2 Power Station</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -18088,7 +18094,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>BRAEMAR5</t>
+          <t>BRAEMAR7</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -18204,12 +18210,12 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>STAPYLTON1</t>
+          <t>RPCG</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Stapylton Renewable Energy Facility</t>
+          <t>Rocky Point Cogeneration Plant</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
